--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffin/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE9EC581-E5E3-234B-B6ED-3968D609EEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC095F02-9BBC-1F4A-AFA2-355DEEF9F2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1420" yWindow="760" windowWidth="28040" windowHeight="17440" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
@@ -134,9 +134,6 @@
     <t>[0.6403 0.4398 0.5579 0.5735 0.2933]</t>
   </si>
   <si>
-    <t>[ 0.6436 0.4295 0.5954 0.6070 0.1733]</t>
-  </si>
-  <si>
     <t>[0.5480 0.3965 0.6774 0.6647 0.2191]</t>
   </si>
   <si>
@@ -213,6 +210,9 @@
   </si>
   <si>
     <t>[0.6349 0.4800 0.5802 0.6438 0.1862</t>
+  </si>
+  <si>
+    <t>[0.6436 0.4295 0.5954 0.6070 0.1733]</t>
   </si>
 </sst>
 </file>
@@ -273,12 +273,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -711,7 +712,7 @@
         <v>0.1079</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F2" s="3">
         <v>0.39439999999999997</v>
@@ -723,10 +724,10 @@
         <v>8.3400000000000002E-2</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -743,7 +744,7 @@
         <v>0.16309999999999999</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" s="1">
         <v>0.35149999999999998</v>
@@ -755,7 +756,7 @@
         <v>0.2475</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>19</v>
@@ -775,7 +776,7 @@
         <v>0.20369999999999999</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F4" s="1">
         <v>0.38009999999999999</v>
@@ -787,7 +788,7 @@
         <v>0.29380000000000001</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>19</v>
@@ -807,7 +808,7 @@
         <v>0.25069999999999998</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F5" s="1">
         <v>0.28970000000000001</v>
@@ -819,7 +820,7 @@
         <v>0.2984</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>19</v>
@@ -839,7 +840,7 @@
         <v>0.28410000000000002</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F6" s="1">
         <v>0.27810000000000001</v>
@@ -851,7 +852,7 @@
         <v>0.31879999999999997</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>19</v>
@@ -998,8 +999,8 @@
       <c r="D11" s="2">
         <v>0.29549999999999998</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>32</v>
+      <c r="E11" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="F11" s="2">
         <v>0.28589999999999999</v>
@@ -1011,7 +1012,7 @@
         <v>0.3372</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>19</v>
@@ -1031,7 +1032,7 @@
         <v>0.31130000000000002</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F12" s="2">
         <v>0.26140000000000002</v>
@@ -1043,7 +1044,7 @@
         <v>0.3513</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>19</v>
@@ -1255,7 +1256,7 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F19" s="2">
         <v>0.62770000000000004</v>
@@ -1267,7 +1268,7 @@
         <v>0.39350000000000002</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>18</v>
@@ -1287,7 +1288,7 @@
         <v>0.38219999999999998</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F20" s="2">
         <v>0.745</v>
@@ -1299,7 +1300,7 @@
         <v>0.35589999999999999</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>19</v>
@@ -1319,7 +1320,7 @@
         <v>0.37419999999999998</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F21" s="2">
         <v>0.70099999999999996</v>
@@ -1331,7 +1332,7 @@
         <v>0.34499999999999997</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>19</v>
@@ -1351,7 +1352,7 @@
         <v>0.37859999999999999</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F22" s="2">
         <v>0.61350000000000005</v>
@@ -1363,7 +1364,7 @@
         <v>0.3876</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>19</v>
@@ -1383,7 +1384,7 @@
         <v>0.39100000000000001</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F23" s="2">
         <v>0.62390000000000001</v>
@@ -1395,7 +1396,7 @@
         <v>0.38179999999999997</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>19</v>
@@ -1415,7 +1416,7 @@
         <v>0.40699999999999997</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F24" s="2">
         <v>0.62609999999999999</v>
@@ -1427,7 +1428,7 @@
         <v>0.4002</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>19</v>

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffin/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC095F02-9BBC-1F4A-AFA2-355DEEF9F2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8B0A79-1572-8B42-9201-D8F90DB4C007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1420" yWindow="760" windowWidth="28040" windowHeight="17440" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="71">
   <si>
     <t>Epoch</t>
   </si>
@@ -213,13 +213,49 @@
   </si>
   <si>
     <t>[0.6436 0.4295 0.5954 0.6070 0.1733]</t>
+  </si>
+  <si>
+    <t>[0.7339 0.6170 0.7458 0.7243 0.5448]</t>
+  </si>
+  <si>
+    <t>[0.6598 0.4641 0.6799 0.6338 0.5221]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reset </t>
+  </si>
+  <si>
+    <t>[0.6254 0.5028 0.6868 0.6138 0.3962]</t>
+  </si>
+  <si>
+    <t>[0.7036 0.5641 0.7115 0.6913 0.5130]</t>
+  </si>
+  <si>
+    <t>[0.6418 0.4685 0.6593 0.6207 0.2664]</t>
+  </si>
+  <si>
+    <t>[0.6567 0.4268 0.7229 0.6778 0.4692]</t>
+  </si>
+  <si>
+    <t>[0.7477 0.6564 0.7584 0.7563 0.5533]</t>
+  </si>
+  <si>
+    <t>[0.7036 0.5071 0.7158 0.6670 0.5021]</t>
+  </si>
+  <si>
+    <t>[0.7789 0.6816 0.7998 0.7909 0.6044</t>
+  </si>
+  <si>
+    <t>[0.6806 0.4630 0.6961 0.6690 0.5174]</t>
+  </si>
+  <si>
+    <t>Reset, removed scheduler (just using lr=5e-4)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -252,6 +288,12 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF202124"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -279,7 +321,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -651,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FCDFC6-C99C-D343-998E-FFAC6AB50B7A}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
@@ -999,7 +1041,7 @@
       <c r="D11" s="2">
         <v>0.29549999999999998</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" t="s">
         <v>58</v>
       </c>
       <c r="F11" s="2">
@@ -1432,6 +1474,206 @@
       </c>
       <c r="J24" s="1" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>29</v>
+      </c>
+      <c r="B25">
+        <v>0.4002</v>
+      </c>
+      <c r="C25">
+        <v>0.59550000000000003</v>
+      </c>
+      <c r="D25">
+        <v>0.4224</v>
+      </c>
+      <c r="E25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25">
+        <v>0.64470000000000005</v>
+      </c>
+      <c r="G25">
+        <v>0.49480000000000002</v>
+      </c>
+      <c r="H25">
+        <v>0.39560000000000001</v>
+      </c>
+      <c r="I25" t="s">
+        <v>60</v>
+      </c>
+      <c r="J25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="19" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>30</v>
+      </c>
+      <c r="B26">
+        <v>0.48530000000000001</v>
+      </c>
+      <c r="C26">
+        <v>0.54310000000000003</v>
+      </c>
+      <c r="D26">
+        <v>0.39860000000000001</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" s="5">
+        <v>0.67290000000000005</v>
+      </c>
+      <c r="G26" s="5">
+        <v>0.47860000000000003</v>
+      </c>
+      <c r="H26" s="5">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="I26" t="s">
+        <v>62</v>
+      </c>
+      <c r="J26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>31</v>
+      </c>
+      <c r="B27">
+        <v>0.48</v>
+      </c>
+      <c r="C27">
+        <v>0.54039999999999999</v>
+      </c>
+      <c r="D27">
+        <v>0.39879999999999999</v>
+      </c>
+      <c r="E27" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27">
+        <v>0.69350000000000001</v>
+      </c>
+      <c r="G27">
+        <v>0.39889999999999998</v>
+      </c>
+      <c r="H27">
+        <v>0.37440000000000001</v>
+      </c>
+      <c r="I27" t="s">
+        <v>64</v>
+      </c>
+      <c r="J27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>32</v>
+      </c>
+      <c r="B28">
+        <v>0.4234</v>
+      </c>
+      <c r="C28">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="D28">
+        <v>0.41460000000000002</v>
+      </c>
+      <c r="E28" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28">
+        <v>0.66220000000000001</v>
+      </c>
+      <c r="G28">
+        <v>0.50439999999999996</v>
+      </c>
+      <c r="H28">
+        <v>0.3977</v>
+      </c>
+      <c r="I28" t="s">
+        <v>65</v>
+      </c>
+      <c r="J28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>33</v>
+      </c>
+      <c r="B29">
+        <v>0.34749999999999998</v>
+      </c>
+      <c r="C29">
+        <v>0.63460000000000005</v>
+      </c>
+      <c r="D29">
+        <v>0.44059999999999999</v>
+      </c>
+      <c r="E29" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29">
+        <v>0.73399999999999999</v>
+      </c>
+      <c r="G29">
+        <v>0.55859999999999999</v>
+      </c>
+      <c r="H29">
+        <v>0.40279999999999999</v>
+      </c>
+      <c r="I29" t="s">
+        <v>67</v>
+      </c>
+      <c r="J29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>34</v>
+      </c>
+      <c r="B30">
+        <v>0.29239999999999999</v>
+      </c>
+      <c r="C30">
+        <v>0.68289999999999995</v>
+      </c>
+      <c r="D30">
+        <v>0.45950000000000002</v>
+      </c>
+      <c r="E30" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30">
+        <v>0.78769999999999996</v>
+      </c>
+      <c r="G30">
+        <v>0.57050000000000001</v>
+      </c>
+      <c r="H30">
+        <v>0.39689999999999998</v>
+      </c>
+      <c r="I30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>35</v>
+      </c>
+      <c r="J31" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffin/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8B0A79-1572-8B42-9201-D8F90DB4C007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D3BA3D-68B4-5442-B072-A38F6C668E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1420" yWindow="760" windowWidth="28040" windowHeight="17440" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
+    <workbookView xWindow="49500" yWindow="660" windowWidth="18980" windowHeight="20780" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="90">
   <si>
     <t>Epoch</t>
   </si>
@@ -248,14 +248,71 @@
     <t>[0.6806 0.4630 0.6961 0.6690 0.5174]</t>
   </si>
   <si>
-    <t>Reset, removed scheduler (just using lr=5e-4)</t>
+    <t>Reset, removed scheduler (just using lr=5e-4), added data augmentation</t>
+  </si>
+  <si>
+    <t>[0.7539 0.6735 0.7774 0.7587 0.5720]</t>
+  </si>
+  <si>
+    <t>[0.6863 0.4881 0.6977 0.6470 0.5496]</t>
+  </si>
+  <si>
+    <t>[0.7664 0.6632 0.7759 0.7777 0.5836]</t>
+  </si>
+  <si>
+    <t>[0.6797 0.5200 0.7068 0.6636 0.4818]</t>
+  </si>
+  <si>
+    <t>[0.7685 0.6954 0.7837 0.7860 0.5906]</t>
+  </si>
+  <si>
+    <t>[0.6918 0.4809 0.6982 0.6641 0.4036]</t>
+  </si>
+  <si>
+    <t>NO LOSS FUNCTION CHANGE</t>
+  </si>
+  <si>
+    <t>[0.7109 0.5291 0.7005 0.7085 0.3947]</t>
+  </si>
+  <si>
+    <t>[0.6961 0.4692 0.7171 0.6686 0.3433]</t>
+  </si>
+  <si>
+    <t>[0.6778 0.5030 0.6636 0.6627 0.3208]</t>
+  </si>
+  <si>
+    <t>[0.4595 0.4411 0.6557 0.6022 0.3177]</t>
+  </si>
+  <si>
+    <t>[0.6770 0.4880 0.6689 0.6492 0.3358]</t>
+  </si>
+  <si>
+    <t>[0.6149 0.4812 0.6415 0.6425 0.1943]</t>
+  </si>
+  <si>
+    <t>[0.6886 0.5216 0.7002 0.6735 0.3720]</t>
+  </si>
+  <si>
+    <t>[0.6723 0.4460 0.6772 0.6775 0.2954]</t>
+  </si>
+  <si>
+    <t>[0.7115 0.5700 0.7249 0.7044 0.4127]</t>
+  </si>
+  <si>
+    <t>[0.6818 0.4789 0.7276 0.6658 0.3181]</t>
+  </si>
+  <si>
+    <t>[0.7316 0.5922 0.7621 0.7291 0.4860]</t>
+  </si>
+  <si>
+    <t>[0.6502 0.5237 0.6735 0.6631 0.3581]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -288,12 +345,6 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF202124"/>
-      <name val="Courier New"/>
-      <family val="1"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -321,12 +372,144 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -358,19 +541,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B743446D-D588-D642-91D0-E5B087766D29}" name="Table1" displayName="Table1" ref="A1:J1048576" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B743446D-D588-D642-91D0-E5B087766D29}" name="Table1" displayName="Table1" ref="A1:J1048576" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:J1048576" xr:uid="{B743446D-D588-D642-91D0-E5B087766D29}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{F6540BAE-4342-0C4D-9A11-D9670848F79D}" name="Epoch"/>
-    <tableColumn id="2" xr3:uid="{06BB7BA3-4DA8-B441-A904-C148F8C004F5}" name="Train loss"/>
-    <tableColumn id="3" xr3:uid="{942ACDBF-0AEA-0345-83EA-B7637B2D3826}" name="Train Accuracy"/>
-    <tableColumn id="4" xr3:uid="{6173A4A8-3F60-7A43-9BBB-37DAC9486BA5}" name="Train Avg F1 Score"/>
-    <tableColumn id="5" xr3:uid="{5FB06B01-3C9E-F749-ABAB-859A4A92F523}" name="Train Label F1 Scores"/>
-    <tableColumn id="6" xr3:uid="{2A8B0A23-6BC6-AE44-90B2-FCBB6182BEAC}" name="Val Loss"/>
-    <tableColumn id="7" xr3:uid="{E09BA5C4-B7E6-DE48-97DC-3C5F6DE1E184}" name="Val Accuracy"/>
-    <tableColumn id="8" xr3:uid="{935DED29-32DD-B244-A68F-C14E6283382A}" name="Val Avg F1 Score"/>
-    <tableColumn id="9" xr3:uid="{7302E524-4E7B-704E-A799-9A4E36F7E5FD}" name="Val Label F1 Scores"/>
-    <tableColumn id="10" xr3:uid="{4B02DA30-8084-2347-A35C-657B957ABF28}" name="Notes"/>
+    <tableColumn id="1" xr3:uid="{F6540BAE-4342-0C4D-9A11-D9670848F79D}" name="Epoch" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{06BB7BA3-4DA8-B441-A904-C148F8C004F5}" name="Train loss" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{942ACDBF-0AEA-0345-83EA-B7637B2D3826}" name="Train Accuracy" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{6173A4A8-3F60-7A43-9BBB-37DAC9486BA5}" name="Train Avg F1 Score" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{5FB06B01-3C9E-F749-ABAB-859A4A92F523}" name="Train Label F1 Scores" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{2A8B0A23-6BC6-AE44-90B2-FCBB6182BEAC}" name="Val Loss" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{E09BA5C4-B7E6-DE48-97DC-3C5F6DE1E184}" name="Val Accuracy" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{935DED29-32DD-B244-A68F-C14E6283382A}" name="Val Avg F1 Score" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{7302E524-4E7B-704E-A799-9A4E36F7E5FD}" name="Val Label F1 Scores" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{4B02DA30-8084-2347-A35C-657B957ABF28}" name="Notes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -693,19 +876,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FCDFC6-C99C-D343-998E-FFAC6AB50B7A}">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.5" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="3" width="15.5" customWidth="1"/>
-    <col min="4" max="4" width="18.1640625" customWidth="1"/>
-    <col min="5" max="5" width="32" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="14.1640625" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="31.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.33203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -1041,7 +1224,7 @@
       <c r="D11" s="2">
         <v>0.29549999999999998</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F11" s="2">
@@ -1477,203 +1660,462 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25">
+      <c r="A25" s="1">
         <v>29</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="1">
         <v>0.4002</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="1">
         <v>0.59550000000000003</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="1">
         <v>0.4224</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <v>0.64470000000000005</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <v>0.49480000000000002</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>0.39560000000000001</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="19" x14ac:dyDescent="0.25">
-      <c r="A26">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
         <v>30</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="1">
         <v>0.48530000000000001</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>0.54310000000000003</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="1">
         <v>0.39860000000000001</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="2">
         <v>0.67290000000000005</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="2">
         <v>0.47860000000000003</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="2">
         <v>0.38400000000000001</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A27">
+      <c r="A27" s="1">
         <v>31</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="1">
         <v>0.48</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="1">
         <v>0.54039999999999999</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
         <v>0.39879999999999999</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="1">
         <v>0.69350000000000001</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <v>0.39889999999999998</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>0.37440000000000001</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28">
+      <c r="A28" s="1">
         <v>32</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="1">
         <v>0.4234</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="1">
         <v>0.57399999999999995</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="1">
         <v>0.41460000000000002</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="1">
         <v>0.66220000000000001</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <v>0.50439999999999996</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>0.3977</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29">
+      <c r="A29" s="1">
         <v>33</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="1">
         <v>0.34749999999999998</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>0.63460000000000005</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="1">
         <v>0.44059999999999999</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="1">
         <v>0.73399999999999999</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="1">
         <v>0.55859999999999999</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>0.40279999999999999</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30">
+      <c r="A30" s="1">
         <v>34</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="1">
         <v>0.29239999999999999</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="1">
         <v>0.68289999999999995</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="1">
         <v>0.45950000000000002</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="1">
         <v>0.78769999999999996</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="1">
         <v>0.57050000000000001</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>0.39689999999999998</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J30" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31">
+      <c r="A31" s="1">
         <v>35</v>
+      </c>
+      <c r="B31" s="1">
+        <v>0.32750000000000001</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0.65149999999999997</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0.44790000000000002</v>
+      </c>
+      <c r="E31" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0.78239999999999998</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0.55879999999999996</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0.39550000000000002</v>
+      </c>
+      <c r="I31" t="s">
+        <v>72</v>
       </c>
       <c r="J31" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>36</v>
+      </c>
+      <c r="B32" s="1">
+        <v>0.3125</v>
+      </c>
+      <c r="C32" s="1">
+        <v>0.66400000000000003</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0.4501</v>
+      </c>
+      <c r="E32" t="s">
+        <v>73</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0.82899999999999996</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0.56169999999999998</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0.40010000000000001</v>
+      </c>
+      <c r="I32" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>37</v>
+      </c>
+      <c r="B33" s="1">
+        <v>0.30509999999999998</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0.6744</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0.45369999999999999</v>
+      </c>
+      <c r="E33" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0.84889999999999999</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0.56889999999999996</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0.39950000000000002</v>
+      </c>
+      <c r="I33" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>23</v>
+      </c>
+      <c r="B34" s="1">
+        <v>0.22159999999999999</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0.64910000000000001</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0.3594</v>
+      </c>
+      <c r="E34" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34">
+        <v>0.27179999999999999</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0.61570000000000003</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0.39939999999999998</v>
+      </c>
+      <c r="I34" t="s">
+        <v>79</v>
+      </c>
+      <c r="J34" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>24</v>
+      </c>
+      <c r="B35" s="1">
+        <v>0.246</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.62329999999999997</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0.33789999999999998</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0.29949999999999999</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.54779999999999995</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0.33360000000000001</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>25</v>
+      </c>
+      <c r="B36" s="1">
+        <v>0.2457</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.625</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0.25650000000000001</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0.61409999999999998</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0.33729999999999999</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" s="5">
+        <v>26</v>
+      </c>
+      <c r="B37" s="1">
+        <v>0.23089999999999999</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0.64019999999999999</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0.35139999999999999</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0.25280000000000002</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.62519999999999998</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0.35220000000000001</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>27</v>
+      </c>
+      <c r="B38" s="1">
+        <v>0.2089</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0.66779999999999995</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0.37290000000000001</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0.2535</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0.63529999999999998</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0.371</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>28</v>
+      </c>
+      <c r="B39" s="1">
+        <v>0.18740000000000001</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.69379999999999997</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0.39050000000000001</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0.25540000000000002</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0.36770000000000003</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffin/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D3BA3D-68B4-5442-B072-A38F6C668E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A11DFE4-1605-D94E-BC01-5FAA3D8ECA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="49500" yWindow="660" windowWidth="18980" windowHeight="20780" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17600" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="ResNet" sheetId="1" r:id="rId1"/>
+    <sheet name="ResNet_Different_Loss" sheetId="3" r:id="rId2"/>
+    <sheet name="EfficientNet" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="112">
   <si>
     <t>Epoch</t>
   </si>
@@ -306,13 +308,79 @@
   </si>
   <si>
     <t>[0.6502 0.5237 0.6735 0.6631 0.3581]</t>
+  </si>
+  <si>
+    <t>[0.7379 0.6026 0.7409 0.7255 0.4800]</t>
+  </si>
+  <si>
+    <t>RESET</t>
+  </si>
+  <si>
+    <t>[0.6705 0.4546 0.7264 0.6556 0.4177]</t>
+  </si>
+  <si>
+    <t>[0.3194 0.2014 0.3460 0.3098 0.1141]</t>
+  </si>
+  <si>
+    <t>[0.2456 0.1386 0.3847 0.3327 0.1135]</t>
+  </si>
+  <si>
+    <t>[0.6432 0.4849 0.6871 0.6650 0.3518]</t>
+  </si>
+  <si>
+    <t>[0.7004 0.5522 0.7025 0.6949 0.4321]</t>
+  </si>
+  <si>
+    <t>[0.6629 0.4842 0.6541 0.6643 0.2940]</t>
+  </si>
+  <si>
+    <t>[0.5147 0.3381 0.4685 0.4380 0.1671]</t>
+  </si>
+  <si>
+    <t>[0.5670 0.3443 0.5166 0.4639 0.2070]</t>
+  </si>
+  <si>
+    <t>[0.6244 0.4028 0.5557 0.5624 0.2413]</t>
+  </si>
+  <si>
+    <t>[0.6421 0.3296 0.5957 0.5105 0.3766]</t>
+  </si>
+  <si>
+    <t>[0.7368 0.5921 0.7486 0.7314 0.4934]</t>
+  </si>
+  <si>
+    <t>[0.6797 0.5270 0.6462 0.6699 0.3669]</t>
+  </si>
+  <si>
+    <t>[0.7775 0.6496 0.8010 0.7729 0.5702]</t>
+  </si>
+  <si>
+    <t>[0.6677 0.5020 0.6907 0.6605 0.3695]</t>
+  </si>
+  <si>
+    <t>[0.6430 0.4120 0.6010 0.5847 0.2962]</t>
+  </si>
+  <si>
+    <t>[0.6354 0.3826 0.6059 0.6499 0.3939]</t>
+  </si>
+  <si>
+    <t>[0.6462 0.4341 0.6233 0.6107 0.3284]</t>
+  </si>
+  <si>
+    <t>[0.6184 0.4307 0.6627 0.6344 0.4677]</t>
+  </si>
+  <si>
+    <t>[0.6565 0.4257 0.6285 0.6139 0.3478]</t>
+  </si>
+  <si>
+    <t>[0.6573 0.4490 0.6314 0.6493 0.3404]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -345,16 +413,29 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202124"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -362,22 +443,216 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -541,19 +816,38 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B743446D-D588-D642-91D0-E5B087766D29}" name="Table1" displayName="Table1" ref="A1:J1048576" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J1048576" xr:uid="{B743446D-D588-D642-91D0-E5B087766D29}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B743446D-D588-D642-91D0-E5B087766D29}" name="Table1" displayName="Table1" ref="A1:J1048561" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+  <autoFilter ref="A1:J1048561" xr:uid="{B743446D-D588-D642-91D0-E5B087766D29}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{F6540BAE-4342-0C4D-9A11-D9670848F79D}" name="Epoch" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{06BB7BA3-4DA8-B441-A904-C148F8C004F5}" name="Train loss" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{942ACDBF-0AEA-0345-83EA-B7637B2D3826}" name="Train Accuracy" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{6173A4A8-3F60-7A43-9BBB-37DAC9486BA5}" name="Train Avg F1 Score" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{5FB06B01-3C9E-F749-ABAB-859A4A92F523}" name="Train Label F1 Scores" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{2A8B0A23-6BC6-AE44-90B2-FCBB6182BEAC}" name="Val Loss" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{E09BA5C4-B7E6-DE48-97DC-3C5F6DE1E184}" name="Val Accuracy" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{935DED29-32DD-B244-A68F-C14E6283382A}" name="Val Avg F1 Score" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{7302E524-4E7B-704E-A799-9A4E36F7E5FD}" name="Val Label F1 Scores" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{4B02DA30-8084-2347-A35C-657B957ABF28}" name="Notes" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{F6540BAE-4342-0C4D-9A11-D9670848F79D}" name="Epoch" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{06BB7BA3-4DA8-B441-A904-C148F8C004F5}" name="Train loss" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{942ACDBF-0AEA-0345-83EA-B7637B2D3826}" name="Train Accuracy" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{6173A4A8-3F60-7A43-9BBB-37DAC9486BA5}" name="Train Avg F1 Score" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{5FB06B01-3C9E-F749-ABAB-859A4A92F523}" name="Train Label F1 Scores" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{2A8B0A23-6BC6-AE44-90B2-FCBB6182BEAC}" name="Val Loss" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{E09BA5C4-B7E6-DE48-97DC-3C5F6DE1E184}" name="Val Accuracy" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{935DED29-32DD-B244-A68F-C14E6283382A}" name="Val Avg F1 Score" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{7302E524-4E7B-704E-A799-9A4E36F7E5FD}" name="Val Label F1 Scores" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{4B02DA30-8084-2347-A35C-657B957ABF28}" name="Notes" dataDxfId="12"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5DD83FD9-89CA-124F-AF15-96A004707A9C}" name="Table13" displayName="Table13" ref="A1:J1048576" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J1048576" xr:uid="{5DD83FD9-89CA-124F-AF15-96A004707A9C}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{3FC30D7F-518D-534E-A701-EED09A365707}" name="Epoch" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{CEF86F27-BE8A-DC47-ADB7-692F2DFDC6CF}" name="Train loss" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{954B06E9-FC87-3245-9551-072D917FCB79}" name="Train Accuracy" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{457DCAE2-DBF1-1F47-864A-307B38880DD3}" name="Train Avg F1 Score" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{308EF520-141D-C94A-8623-02F49095423C}" name="Train Label F1 Scores" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{69F3F83D-5D1A-B344-87C2-1A84C73D5447}" name="Val Loss" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{3413DEEE-B2D5-C14B-88B1-E8FE8E355848}" name="Val Accuracy" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{096A4E53-7E2C-2440-9E6A-31A91FB89FDB}" name="Val Avg F1 Score" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{9CCA6081-74FF-C447-91BC-2CB33DEB959F}" name="Val Label F1 Scores" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{3B962AD9-3C96-3D49-9243-398E4A0F6FE2}" name="Notes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -876,7 +1170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FCDFC6-C99C-D343-998E-FFAC6AB50B7A}">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5" style="1" customWidth="1"/>
@@ -1472,191 +1766,176 @@
         <v>23</v>
       </c>
       <c r="B19" s="1">
-        <v>0.49149999999999999</v>
-      </c>
-      <c r="C19" s="2">
-        <v>0.57479999999999998</v>
-      </c>
-      <c r="D19" s="2">
-        <v>0.40400000000000003</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0.62770000000000004</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0.47049999999999997</v>
-      </c>
-      <c r="H19" s="2">
-        <v>0.39350000000000002</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>18</v>
+        <v>0.22159999999999999</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.64910000000000001</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.3594</v>
+      </c>
+      <c r="E19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19">
+        <v>0.27179999999999999</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0.61570000000000003</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0.39939999999999998</v>
+      </c>
+      <c r="I19" t="s">
+        <v>79</v>
+      </c>
+      <c r="J19" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>24</v>
       </c>
-      <c r="B20" s="2">
-        <v>0.53510000000000002</v>
-      </c>
-      <c r="C20" s="2">
-        <v>0.5081</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0.38219999999999998</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0.745</v>
-      </c>
-      <c r="G20" s="2">
-        <v>0.29399999999999998</v>
-      </c>
-      <c r="H20" s="2">
-        <v>0.35589999999999999</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>19</v>
+      <c r="B20" s="1">
+        <v>0.246</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.62329999999999997</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.33789999999999998</v>
+      </c>
+      <c r="E20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0.29949999999999999</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0.54779999999999995</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0.33360000000000001</v>
+      </c>
+      <c r="I20" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>25</v>
       </c>
-      <c r="B21" s="2">
-        <v>0.55800000000000005</v>
-      </c>
-      <c r="C21" s="2">
-        <v>0.49440000000000001</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0.37419999999999998</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0.70099999999999996</v>
-      </c>
-      <c r="G21" s="2">
-        <v>0.53680000000000005</v>
-      </c>
-      <c r="H21" s="2">
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>19</v>
+      <c r="B21" s="1">
+        <v>0.2457</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.625</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="E21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0.25650000000000001</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.61409999999999998</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0.33729999999999999</v>
+      </c>
+      <c r="I21" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
+      <c r="A22">
         <v>26</v>
       </c>
-      <c r="B22" s="2">
-        <v>0.54259999999999997</v>
-      </c>
-      <c r="C22" s="2">
-        <v>0.50929999999999997</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0.37859999999999999</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0.61350000000000005</v>
-      </c>
-      <c r="G22" s="2">
-        <v>0.44040000000000001</v>
-      </c>
-      <c r="H22" s="2">
-        <v>0.3876</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>19</v>
+      <c r="B22" s="1">
+        <v>0.23089999999999999</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.64019999999999999</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.35139999999999999</v>
+      </c>
+      <c r="E22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0.25280000000000002</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0.62519999999999998</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0.35220000000000001</v>
+      </c>
+      <c r="I22" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>27</v>
       </c>
-      <c r="B23" s="2">
-        <v>0.50360000000000005</v>
-      </c>
-      <c r="C23" s="2">
-        <v>0.52810000000000001</v>
-      </c>
-      <c r="D23" s="2">
-        <v>0.39100000000000001</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0.62390000000000001</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0.57099999999999995</v>
-      </c>
-      <c r="H23" s="2">
-        <v>0.38179999999999997</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>19</v>
+      <c r="B23" s="1">
+        <v>0.2089</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.66779999999999995</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0.37290000000000001</v>
+      </c>
+      <c r="E23" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0.2535</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0.63529999999999998</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0.371</v>
+      </c>
+      <c r="I23" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>28</v>
       </c>
-      <c r="B24" s="2">
-        <v>0.44879999999999998</v>
-      </c>
-      <c r="C24" s="2">
-        <v>0.56630000000000003</v>
-      </c>
-      <c r="D24" s="2">
-        <v>0.40699999999999997</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F24" s="2">
-        <v>0.62609999999999999</v>
-      </c>
-      <c r="G24" s="2">
-        <v>0.54910000000000003</v>
-      </c>
-      <c r="H24" s="2">
-        <v>0.4002</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>19</v>
+      <c r="B24" s="1">
+        <v>0.18740000000000001</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0.69379999999999997</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.39050000000000001</v>
+      </c>
+      <c r="E24" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0.25540000000000002</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0.36770000000000003</v>
+      </c>
+      <c r="I24" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -1664,31 +1943,31 @@
         <v>29</v>
       </c>
       <c r="B25" s="1">
-        <v>0.4002</v>
+        <v>0.19489999999999999</v>
       </c>
       <c r="C25" s="1">
-        <v>0.59550000000000003</v>
+        <v>0.6381</v>
       </c>
       <c r="D25" s="1">
-        <v>0.4224</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>59</v>
+        <v>0.3861</v>
+      </c>
+      <c r="E25" t="s">
+        <v>90</v>
       </c>
       <c r="F25" s="1">
-        <v>0.64470000000000005</v>
+        <v>0.25890000000000002</v>
       </c>
       <c r="G25" s="1">
-        <v>0.49480000000000002</v>
+        <v>0.62239999999999995</v>
       </c>
       <c r="H25" s="1">
-        <v>0.39560000000000001</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>61</v>
+        <v>0.37990000000000002</v>
+      </c>
+      <c r="I25" t="s">
+        <v>92</v>
+      </c>
+      <c r="J25" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -1696,31 +1975,28 @@
         <v>30</v>
       </c>
       <c r="B26" s="1">
-        <v>0.48530000000000001</v>
+        <v>0.22420000000000001</v>
       </c>
       <c r="C26" s="1">
-        <v>0.54310000000000003</v>
+        <v>0.64929999999999999</v>
       </c>
       <c r="D26" s="1">
-        <v>0.39860000000000001</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0.67290000000000005</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0.47860000000000003</v>
-      </c>
-      <c r="H26" s="2">
-        <v>0.38400000000000001</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>19</v>
+        <v>0.35909999999999997</v>
+      </c>
+      <c r="E26" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0.28720000000000001</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0.3664</v>
+      </c>
+      <c r="I26" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -1728,31 +2004,28 @@
         <v>31</v>
       </c>
       <c r="B27" s="1">
-        <v>0.48</v>
+        <v>0.2157</v>
       </c>
       <c r="C27" s="1">
-        <v>0.54039999999999999</v>
+        <v>0.65759999999999996</v>
       </c>
       <c r="D27" s="1">
-        <v>0.39879999999999999</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>63</v>
+        <v>0.36670000000000003</v>
+      </c>
+      <c r="E27" t="s">
+        <v>96</v>
       </c>
       <c r="F27" s="1">
-        <v>0.69350000000000001</v>
+        <v>0.26269999999999999</v>
       </c>
       <c r="G27" s="1">
-        <v>0.39889999999999998</v>
+        <v>0.62360000000000004</v>
       </c>
       <c r="H27" s="1">
-        <v>0.37440000000000001</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>19</v>
+        <v>0.3543</v>
+      </c>
+      <c r="I27" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
@@ -1760,31 +2033,28 @@
         <v>32</v>
       </c>
       <c r="B28" s="1">
-        <v>0.4234</v>
+        <v>0.18779999999999999</v>
       </c>
       <c r="C28" s="1">
-        <v>0.57399999999999995</v>
+        <v>0.68899999999999995</v>
       </c>
       <c r="D28" s="1">
-        <v>0.41460000000000002</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>65</v>
+        <v>0.39050000000000001</v>
+      </c>
+      <c r="E28" t="s">
+        <v>102</v>
       </c>
       <c r="F28" s="1">
-        <v>0.66220000000000001</v>
+        <v>0.26989999999999997</v>
       </c>
       <c r="G28" s="1">
-        <v>0.50439999999999996</v>
+        <v>0.62490000000000001</v>
       </c>
       <c r="H28" s="1">
-        <v>0.3977</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>19</v>
+        <v>0.36580000000000001</v>
+      </c>
+      <c r="I28" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
@@ -1792,331 +2062,880 @@
         <v>33</v>
       </c>
       <c r="B29" s="1">
+        <v>0.15640000000000001</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0.745</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0.42259999999999998</v>
+      </c>
+      <c r="E29" t="s">
+        <v>104</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0.28029999999999999</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0.62039999999999995</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="I29" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E03FEB-F26A-6948-8F66-30F9CC31F284}">
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="7">
+        <v>23</v>
+      </c>
+      <c r="B1" s="6">
+        <v>0.49149999999999999</v>
+      </c>
+      <c r="C1" s="11">
+        <v>0.57479999999999998</v>
+      </c>
+      <c r="D1" s="11">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="11">
+        <v>0.62770000000000004</v>
+      </c>
+      <c r="G1" s="11">
+        <v>0.47049999999999997</v>
+      </c>
+      <c r="H1" s="11">
+        <v>0.39350000000000002</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="12">
+        <v>24</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.53510000000000002</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.5081</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.38219999999999998</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.745</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="H2" s="13">
+        <v>0.35589999999999999</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="7">
+        <v>25</v>
+      </c>
+      <c r="B3" s="11">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="C3" s="11">
+        <v>0.49440000000000001</v>
+      </c>
+      <c r="D3" s="11">
+        <v>0.37419999999999998</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="11">
+        <v>0.70099999999999996</v>
+      </c>
+      <c r="G3" s="11">
+        <v>0.53680000000000005</v>
+      </c>
+      <c r="H3" s="11">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="12">
+        <v>26</v>
+      </c>
+      <c r="B4" s="13">
+        <v>0.54259999999999997</v>
+      </c>
+      <c r="C4" s="13">
+        <v>0.50929999999999997</v>
+      </c>
+      <c r="D4" s="13">
+        <v>0.37859999999999999</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="13">
+        <v>0.61350000000000005</v>
+      </c>
+      <c r="G4" s="13">
+        <v>0.44040000000000001</v>
+      </c>
+      <c r="H4" s="13">
+        <v>0.3876</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="7">
+        <v>27</v>
+      </c>
+      <c r="B5" s="11">
+        <v>0.50360000000000005</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0.52810000000000001</v>
+      </c>
+      <c r="D5" s="11">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="11">
+        <v>0.62390000000000001</v>
+      </c>
+      <c r="G5" s="11">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="H5" s="11">
+        <v>0.38179999999999997</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="12">
+        <v>28</v>
+      </c>
+      <c r="B6" s="13">
+        <v>0.44879999999999998</v>
+      </c>
+      <c r="C6" s="13">
+        <v>0.56630000000000003</v>
+      </c>
+      <c r="D6" s="13">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="13">
+        <v>0.62609999999999999</v>
+      </c>
+      <c r="G6" s="13">
+        <v>0.54910000000000003</v>
+      </c>
+      <c r="H6" s="13">
+        <v>0.4002</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="7">
+        <v>29</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0.4002</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.59550000000000003</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.4224</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.64470000000000005</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.49480000000000002</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.39560000000000001</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="12">
+        <v>30</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0.48530000000000001</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0.54310000000000003</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.39860000000000001</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="13">
+        <v>0.67290000000000005</v>
+      </c>
+      <c r="G8" s="13">
+        <v>0.47860000000000003</v>
+      </c>
+      <c r="H8" s="13">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="7">
+        <v>31</v>
+      </c>
+      <c r="B9" s="6">
+        <v>0.48</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.54039999999999999</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.39879999999999999</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.69350000000000001</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.39889999999999998</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.37440000000000001</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="12">
+        <v>32</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0.4234</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0.41460000000000002</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0.66220000000000001</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0.50439999999999996</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0.3977</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="7">
+        <v>33</v>
+      </c>
+      <c r="B11" s="6">
         <v>0.34749999999999998</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C11" s="6">
         <v>0.63460000000000005</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D11" s="6">
         <v>0.44059999999999999</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E11" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F11" s="6">
         <v>0.73399999999999999</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G11" s="6">
         <v>0.55859999999999999</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H11" s="6">
         <v>0.40279999999999999</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I11" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J11" s="8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="12">
         <v>34</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B12" s="5">
         <v>0.29239999999999999</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C12" s="5">
         <v>0.68289999999999995</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D12" s="5">
         <v>0.45950000000000002</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E12" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F12" s="5">
         <v>0.78769999999999996</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G12" s="5">
         <v>0.57050000000000001</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H12" s="5">
         <v>0.39689999999999998</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I12" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="J12" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" s="1">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="7">
         <v>35</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B13" s="6">
         <v>0.32750000000000001</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C13" s="6">
         <v>0.65149999999999997</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D13" s="6">
         <v>0.44790000000000002</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E13" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F13" s="6">
         <v>0.78239999999999998</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G13" s="6">
         <v>0.55879999999999996</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H13" s="6">
         <v>0.39550000000000002</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I13" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J13" s="8" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32" s="1">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="12">
         <v>36</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B14" s="5">
         <v>0.3125</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C14" s="5">
         <v>0.66400000000000003</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D14" s="5">
         <v>0.4501</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E14" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F14" s="5">
         <v>0.82899999999999996</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G14" s="5">
         <v>0.56169999999999998</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H14" s="5">
         <v>0.40010000000000001</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I14" s="5" t="s">
         <v>74</v>
       </c>
+      <c r="J14" s="9"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="7">
+        <v>37</v>
+      </c>
+      <c r="B15" s="6">
+        <v>0.30509999999999998</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.6744</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.45369999999999999</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0.84889999999999999</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0.56889999999999996</v>
+      </c>
+      <c r="H15" s="6">
+        <v>0.39950000000000002</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J15" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B641F396-8762-B74C-B488-26FE674E428C}">
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="31.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.33203125" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1.2754000000000001</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="E2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1.1268</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1.06E-2</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0.23230000000000001</v>
+      </c>
+      <c r="I2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1.129</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.1482</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.25269999999999998</v>
+      </c>
+      <c r="E3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.91559999999999997</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.33529999999999999</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.2293</v>
+      </c>
+      <c r="I3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1.1089</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.28460000000000002</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.29170000000000001</v>
+      </c>
+      <c r="E4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.81120000000000003</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.29380000000000001</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.32129999999999997</v>
+      </c>
+      <c r="I4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.97319999999999995</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.32979999999999998</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.3155</v>
+      </c>
+      <c r="E5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.71340000000000003</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.41170000000000001</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.34920000000000001</v>
+      </c>
+      <c r="I5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.95350000000000001</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.35759999999999997</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.33100000000000002</v>
+      </c>
+      <c r="E6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.69010000000000005</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.50619999999999998</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.315</v>
+      </c>
+      <c r="I6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.94389999999999996</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.71209999999999996</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.46129999999999999</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.33069999999999999</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E32"/>
+      <c r="I32"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" s="1">
-        <v>37</v>
-      </c>
-      <c r="B33" s="1">
-        <v>0.30509999999999998</v>
-      </c>
-      <c r="C33" s="1">
-        <v>0.6744</v>
-      </c>
-      <c r="D33" s="1">
-        <v>0.45369999999999999</v>
-      </c>
-      <c r="E33" t="s">
-        <v>75</v>
-      </c>
-      <c r="F33" s="1">
-        <v>0.84889999999999999</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0.56889999999999996</v>
-      </c>
-      <c r="H33" s="1">
-        <v>0.39950000000000002</v>
-      </c>
-      <c r="I33" t="s">
-        <v>76</v>
-      </c>
+      <c r="E33"/>
+      <c r="I33"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A34" s="1">
-        <v>23</v>
-      </c>
-      <c r="B34" s="1">
-        <v>0.22159999999999999</v>
-      </c>
-      <c r="C34" s="1">
-        <v>0.64910000000000001</v>
-      </c>
-      <c r="D34" s="1">
-        <v>0.3594</v>
-      </c>
-      <c r="E34" t="s">
-        <v>78</v>
-      </c>
-      <c r="F34">
-        <v>0.27179999999999999</v>
-      </c>
-      <c r="G34" s="1">
-        <v>0.61570000000000003</v>
-      </c>
-      <c r="H34" s="1">
-        <v>0.39939999999999998</v>
-      </c>
-      <c r="I34" t="s">
-        <v>79</v>
-      </c>
-      <c r="J34" t="s">
-        <v>77</v>
-      </c>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="I34"/>
+      <c r="J34"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A35" s="1">
-        <v>24</v>
-      </c>
-      <c r="B35" s="1">
-        <v>0.246</v>
-      </c>
-      <c r="C35" s="1">
-        <v>0.62329999999999997</v>
-      </c>
-      <c r="D35" s="1">
-        <v>0.33789999999999998</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F35" s="1">
-        <v>0.29949999999999999</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0.54779999999999995</v>
-      </c>
-      <c r="H35" s="1">
-        <v>0.33360000000000001</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="E35"/>
+      <c r="I35"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36" s="1">
-        <v>25</v>
-      </c>
-      <c r="B36" s="1">
-        <v>0.2457</v>
-      </c>
-      <c r="C36" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="D36" s="1">
-        <v>0.34</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F36" s="1">
-        <v>0.25650000000000001</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0.61409999999999998</v>
-      </c>
-      <c r="H36" s="1">
-        <v>0.33729999999999999</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>83</v>
-      </c>
+      <c r="E36"/>
+      <c r="I36"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" s="5">
-        <v>26</v>
-      </c>
-      <c r="B37" s="1">
-        <v>0.23089999999999999</v>
-      </c>
-      <c r="C37" s="1">
-        <v>0.64019999999999999</v>
-      </c>
-      <c r="D37" s="1">
-        <v>0.35139999999999999</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F37" s="1">
-        <v>0.25280000000000002</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0.62519999999999998</v>
-      </c>
-      <c r="H37" s="1">
-        <v>0.35220000000000001</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>85</v>
-      </c>
+      <c r="A37"/>
+      <c r="E37"/>
+      <c r="I37"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38" s="1">
-        <v>27</v>
-      </c>
-      <c r="B38" s="1">
-        <v>0.2089</v>
-      </c>
-      <c r="C38" s="1">
-        <v>0.66779999999999995</v>
-      </c>
-      <c r="D38" s="1">
-        <v>0.37290000000000001</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F38" s="1">
-        <v>0.2535</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0.63529999999999998</v>
-      </c>
-      <c r="H38" s="1">
-        <v>0.371</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>87</v>
-      </c>
+      <c r="E38"/>
+      <c r="I38"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39" s="1">
-        <v>28</v>
-      </c>
-      <c r="B39" s="1">
-        <v>0.18740000000000001</v>
-      </c>
-      <c r="C39" s="1">
-        <v>0.69379999999999997</v>
-      </c>
-      <c r="D39" s="1">
-        <v>0.39050000000000001</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F39" s="1">
-        <v>0.25540000000000002</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0.63200000000000001</v>
-      </c>
-      <c r="H39" s="1">
-        <v>0.36770000000000003</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>89</v>
-      </c>
+      <c r="E39"/>
+      <c r="I39"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E40"/>
+      <c r="I40"/>
+      <c r="J40"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffin/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A11DFE4-1605-D94E-BC01-5FAA3D8ECA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25422828-E441-7C40-A459-BB865C6331E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17600" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="113">
   <si>
     <t>Epoch</t>
   </si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t>[0.6573 0.4490 0.6314 0.6493 0.3404]</t>
+  </si>
+  <si>
+    <t>[0.6956 0.5361 0.6956 0.6885 0.4008]</t>
   </si>
 </sst>
 </file>
@@ -1984,7 +1987,7 @@
         <v>0.35909999999999997</v>
       </c>
       <c r="E26" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="F26" s="1">
         <v>0.28720000000000001</v>

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffin/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25422828-E441-7C40-A459-BB865C6331E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF8C550-B507-F442-B289-3D795F529D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17600" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17600" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
   <sheets>
     <sheet name="ResNet" sheetId="1" r:id="rId1"/>
     <sheet name="ResNet_Different_Loss" sheetId="3" r:id="rId2"/>
     <sheet name="EfficientNet" sheetId="2" r:id="rId3"/>
+    <sheet name="EfficientNet-Retrain" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="131">
   <si>
     <t>Epoch</t>
   </si>
@@ -377,13 +378,67 @@
   </si>
   <si>
     <t>[0.6956 0.5361 0.6956 0.6885 0.4008]</t>
+  </si>
+  <si>
+    <t>[0.6775 0.5011 0.6608 0.6510 0.3290]</t>
+  </si>
+  <si>
+    <t>[0.6702 0.4338 0.6478 0.6540 0.3985]</t>
+  </si>
+  <si>
+    <t>[0.6632 0.4465 0.6370 0.6197 0.3556]</t>
+  </si>
+  <si>
+    <t>[0.6913 0.4632 0.6932 0.6814 0.5057]</t>
+  </si>
+  <si>
+    <t>[0.6703 0.4367 0.6623 0.6406 0.3864]</t>
+  </si>
+  <si>
+    <t>[0.6682 0.4218 0.7087 0.6326 0.4488]</t>
+  </si>
+  <si>
+    <t>[0.6762 0.4492 0.6617 0.6486 0.4085]</t>
+  </si>
+  <si>
+    <t>[0.6896 0.4649 0.7128 0.6897 0.5071]</t>
+  </si>
+  <si>
+    <t>[0.6920 0.4641 0.6789 0.6606 0.4303]</t>
+  </si>
+  <si>
+    <t>[0.6909 0.4579 0.6974 0.7039 0.5321]</t>
+  </si>
+  <si>
+    <t>[0.6908 0.4651 0.6904 0.6666 0.4569]</t>
+  </si>
+  <si>
+    <t>[0.7111 0.4155 0.7187 0.6890 0.4976]</t>
+  </si>
+  <si>
+    <t>Learning Rate</t>
+  </si>
+  <si>
+    <t>Training Hamming Loss</t>
+  </si>
+  <si>
+    <t>Val Hamming Loss</t>
+  </si>
+  <si>
+    <t>[0.7218 0.5143 0.7010 0.6783 0.4285]</t>
+  </si>
+  <si>
+    <t>Retraining the model from scratch; decided to have a higher max learning rate, and set a minimum learning rate; set for 50 epochs (easier than later adjustments to the scheduler)</t>
+  </si>
+  <si>
+    <t>[0.7262 0.4360 0.7171 0.7125 0.6434]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -419,6 +474,14 @@
     <font>
       <sz val="12"/>
       <color rgb="FF202124"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -487,26 +550,223 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="39">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -819,38 +1079,60 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B743446D-D588-D642-91D0-E5B087766D29}" name="Table1" displayName="Table1" ref="A1:J1048561" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B743446D-D588-D642-91D0-E5B087766D29}" name="Table1" displayName="Table1" ref="A1:J1048561" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
   <autoFilter ref="A1:J1048561" xr:uid="{B743446D-D588-D642-91D0-E5B087766D29}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{F6540BAE-4342-0C4D-9A11-D9670848F79D}" name="Epoch" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{06BB7BA3-4DA8-B441-A904-C148F8C004F5}" name="Train loss" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{942ACDBF-0AEA-0345-83EA-B7637B2D3826}" name="Train Accuracy" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{6173A4A8-3F60-7A43-9BBB-37DAC9486BA5}" name="Train Avg F1 Score" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{5FB06B01-3C9E-F749-ABAB-859A4A92F523}" name="Train Label F1 Scores" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{2A8B0A23-6BC6-AE44-90B2-FCBB6182BEAC}" name="Val Loss" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{E09BA5C4-B7E6-DE48-97DC-3C5F6DE1E184}" name="Val Accuracy" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{935DED29-32DD-B244-A68F-C14E6283382A}" name="Val Avg F1 Score" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{7302E524-4E7B-704E-A799-9A4E36F7E5FD}" name="Val Label F1 Scores" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{4B02DA30-8084-2347-A35C-657B957ABF28}" name="Notes" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{F6540BAE-4342-0C4D-9A11-D9670848F79D}" name="Epoch" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{06BB7BA3-4DA8-B441-A904-C148F8C004F5}" name="Train loss" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{942ACDBF-0AEA-0345-83EA-B7637B2D3826}" name="Train Accuracy" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{6173A4A8-3F60-7A43-9BBB-37DAC9486BA5}" name="Train Avg F1 Score" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{5FB06B01-3C9E-F749-ABAB-859A4A92F523}" name="Train Label F1 Scores" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{2A8B0A23-6BC6-AE44-90B2-FCBB6182BEAC}" name="Val Loss" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{E09BA5C4-B7E6-DE48-97DC-3C5F6DE1E184}" name="Val Accuracy" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{935DED29-32DD-B244-A68F-C14E6283382A}" name="Val Avg F1 Score" dataDxfId="29"/>
+    <tableColumn id="9" xr3:uid="{7302E524-4E7B-704E-A799-9A4E36F7E5FD}" name="Val Label F1 Scores" dataDxfId="28"/>
+    <tableColumn id="10" xr3:uid="{4B02DA30-8084-2347-A35C-657B957ABF28}" name="Notes" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5DD83FD9-89CA-124F-AF15-96A004707A9C}" name="Table13" displayName="Table13" ref="A1:J1048576" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5DD83FD9-89CA-124F-AF15-96A004707A9C}" name="Table13" displayName="Table13" ref="A1:J1048576" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="A1:J1048576" xr:uid="{5DD83FD9-89CA-124F-AF15-96A004707A9C}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{3FC30D7F-518D-534E-A701-EED09A365707}" name="Epoch" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{CEF86F27-BE8A-DC47-ADB7-692F2DFDC6CF}" name="Train loss" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{954B06E9-FC87-3245-9551-072D917FCB79}" name="Train Accuracy" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{457DCAE2-DBF1-1F47-864A-307B38880DD3}" name="Train Avg F1 Score" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{308EF520-141D-C94A-8623-02F49095423C}" name="Train Label F1 Scores" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{69F3F83D-5D1A-B344-87C2-1A84C73D5447}" name="Val Loss" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{3413DEEE-B2D5-C14B-88B1-E8FE8E355848}" name="Val Accuracy" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{096A4E53-7E2C-2440-9E6A-31A91FB89FDB}" name="Val Avg F1 Score" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{9CCA6081-74FF-C447-91BC-2CB33DEB959F}" name="Val Label F1 Scores" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{3B962AD9-3C96-3D49-9243-398E4A0F6FE2}" name="Notes" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{3FC30D7F-518D-534E-A701-EED09A365707}" name="Epoch" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{CEF86F27-BE8A-DC47-ADB7-692F2DFDC6CF}" name="Train loss" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{954B06E9-FC87-3245-9551-072D917FCB79}" name="Train Accuracy" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{457DCAE2-DBF1-1F47-864A-307B38880DD3}" name="Train Avg F1 Score" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{308EF520-141D-C94A-8623-02F49095423C}" name="Train Label F1 Scores" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{69F3F83D-5D1A-B344-87C2-1A84C73D5447}" name="Val Loss" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{3413DEEE-B2D5-C14B-88B1-E8FE8E355848}" name="Val Accuracy" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{096A4E53-7E2C-2440-9E6A-31A91FB89FDB}" name="Val Avg F1 Score" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{9CCA6081-74FF-C447-91BC-2CB33DEB959F}" name="Val Label F1 Scores" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{3B962AD9-3C96-3D49-9243-398E4A0F6FE2}" name="Notes" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{480E0B5D-91EF-3A43-9756-59D51622B3B6}" name="Table134" displayName="Table134" ref="A1:M1048576" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+  <autoFilter ref="A1:M1048576" xr:uid="{480E0B5D-91EF-3A43-9756-59D51622B3B6}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{23378AFE-7605-0143-847E-6BF4D6EC71F7}" name="Epoch" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{8EE2BBDB-2101-934B-B90C-8BC0CA53A271}" name="Train loss" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{4BD9BDF7-E421-5845-A339-7F6F4835D46B}" name="Train Accuracy" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{BC399B82-1818-C442-8AF5-A5E6ACD4F9AC}" name="Training Hamming Loss" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{207D034B-40D0-4F4F-BE5B-D77D7E850420}" name="Train Avg F1 Score" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{202B1475-7518-8549-B088-D3B90F6F26B0}" name="Train Label F1 Scores" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{F35ACBEE-D3B4-224E-AE25-FDDB59600115}" name="Val Loss" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{81A115D6-3B37-5F44-B83F-76AC38D42D60}" name="Val Accuracy" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{851DD49C-A36C-C843-AA3A-C3B022F3F8B0}" name="Val Hamming Loss" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{5595516A-7F54-DA48-92BA-0C9BBC2D5E7D}" name="Val Avg F1 Score" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{CD169DB8-5572-8149-B688-EEEDBA4E5E0D}" name="Val Label F1 Scores" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{3AA60CBC-B330-0F40-81AA-8B93624B9AD9}" name="Learning Rate" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{0BF429D1-196F-4B4C-8AC4-789B62E96A73}" name="Notes" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2109,22 +2391,22 @@
       <c r="B1" s="6">
         <v>0.49149999999999999</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="10">
         <v>0.57479999999999998</v>
       </c>
-      <c r="D1" s="11">
+      <c r="D1" s="10">
         <v>0.40400000000000003</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="11">
+      <c r="F1" s="10">
         <v>0.62770000000000004</v>
       </c>
-      <c r="G1" s="11">
+      <c r="G1" s="10">
         <v>0.47049999999999997</v>
       </c>
-      <c r="H1" s="11">
+      <c r="H1" s="10">
         <v>0.39350000000000002</v>
       </c>
       <c r="I1" s="6" t="s">
@@ -2135,28 +2417,28 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="12">
+      <c r="A2" s="11">
         <v>24</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="12">
         <v>0.53510000000000002</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>0.5081</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="12">
         <v>0.38219999999999998</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="12">
         <v>0.745</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="12">
         <v>0.29399999999999998</v>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="12">
         <v>0.35589999999999999</v>
       </c>
       <c r="I2" s="5" t="s">
@@ -2170,25 +2452,25 @@
       <c r="A3" s="7">
         <v>25</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="10">
         <v>0.55800000000000005</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>0.49440000000000001</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>0.37419999999999998</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="10">
         <v>0.70099999999999996</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="10">
         <v>0.53680000000000005</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="10">
         <v>0.34499999999999997</v>
       </c>
       <c r="I3" s="6" t="s">
@@ -2199,28 +2481,28 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="12">
+      <c r="A4" s="11">
         <v>26</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="12">
         <v>0.54259999999999997</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="12">
         <v>0.50929999999999997</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>0.37859999999999999</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>0.61350000000000005</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>0.44040000000000001</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>0.3876</v>
       </c>
       <c r="I4" s="5" t="s">
@@ -2234,25 +2516,25 @@
       <c r="A5" s="7">
         <v>27</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <v>0.50360000000000005</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>0.52810000000000001</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>0.39100000000000001</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <v>0.62390000000000001</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
         <v>0.57099999999999995</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="10">
         <v>0.38179999999999997</v>
       </c>
       <c r="I5" s="6" t="s">
@@ -2263,28 +2545,28 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="12">
+      <c r="A6" s="11">
         <v>28</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="12">
         <v>0.44879999999999998</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="12">
         <v>0.56630000000000003</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>0.40699999999999997</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>0.62609999999999999</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <v>0.54910000000000003</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <v>0.4002</v>
       </c>
       <c r="I6" s="5" t="s">
@@ -2327,7 +2609,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="12">
+      <c r="A8" s="11">
         <v>30</v>
       </c>
       <c r="B8" s="5">
@@ -2339,16 +2621,16 @@
       <c r="D8" s="5">
         <v>0.39860000000000001</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <v>0.67290000000000005</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <v>0.47860000000000003</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="12">
         <v>0.38400000000000001</v>
       </c>
       <c r="I8" s="5" t="s">
@@ -2391,7 +2673,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="12">
+      <c r="A10" s="11">
         <v>32</v>
       </c>
       <c r="B10" s="5">
@@ -2455,7 +2737,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="12">
+      <c r="A12" s="11">
         <v>34</v>
       </c>
       <c r="B12" s="5">
@@ -2519,7 +2801,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="12">
+      <c r="A14" s="11">
         <v>36</v>
       </c>
       <c r="B14" s="5">
@@ -2585,7 +2867,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B641F396-8762-B74C-B488-26FE674E428C}">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5" style="1" customWidth="1"/>
@@ -2790,7 +3072,7 @@
       <c r="D7" s="1">
         <v>0.34</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" t="s">
         <v>110</v>
       </c>
       <c r="F7" s="1">
@@ -2802,54 +3084,223 @@
       <c r="H7" s="1">
         <v>0.33069999999999999</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.93899999999999995</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.41820000000000002</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.34439999999999998</v>
+      </c>
+      <c r="E8" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.7006</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.48430000000000001</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.3422</v>
+      </c>
+      <c r="I8" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.93189999999999995</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.37559999999999999</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.34439999999999998</v>
+      </c>
+      <c r="E9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.62919999999999998</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.50460000000000005</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.39460000000000001</v>
+      </c>
+      <c r="I9" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.91710000000000003</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.39069999999999999</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.3589</v>
+      </c>
+      <c r="E10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.64690000000000003</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.4768</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.3735</v>
+      </c>
+      <c r="I10" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.90580000000000005</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.4088</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0.3629</v>
+      </c>
+      <c r="E11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.38040000000000002</v>
+      </c>
+      <c r="I11" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.89070000000000005</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.43719999999999998</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.37219999999999998</v>
+      </c>
+      <c r="E12" t="s">
+        <v>121</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.61470000000000002</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.51139999999999997</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.3947</v>
+      </c>
+      <c r="I12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0.87929999999999997</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.44900000000000001</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.37990000000000002</v>
+      </c>
+      <c r="E13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0.61160000000000003</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0.50460000000000005</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0.39140000000000003</v>
+      </c>
+      <c r="I13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -2857,7 +3308,10 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -2865,7 +3319,10 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -2873,7 +3330,10 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -2881,7 +3341,10 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -2889,56 +3352,607 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
       <c r="E31"/>
       <c r="I31"/>
       <c r="J31"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
       <c r="E32"/>
       <c r="I32"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
       <c r="E33"/>
       <c r="I33"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
       <c r="E34"/>
       <c r="F34"/>
       <c r="I34"/>
       <c r="J34"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
       <c r="E35"/>
       <c r="I35"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
       <c r="E36"/>
       <c r="I36"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37"/>
+      <c r="A37">
+        <v>36</v>
+      </c>
       <c r="E37"/>
       <c r="I37"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
       <c r="E38"/>
       <c r="I38"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
       <c r="E39"/>
       <c r="I39"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
       <c r="E40"/>
       <c r="I40"/>
       <c r="J40"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{792EDA06-FC2C-024C-AE8E-C1CCD07C3F11}">
+  <dimension ref="A1:M51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" style="1" customWidth="1"/>
+    <col min="8" max="9" width="14.1640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="31.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.1640625" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0.88149999999999995</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.45839999999999997</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.16930000000000001</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="F2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.63759999999999994</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0.50609999999999999</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0.14860000000000001</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0.3795</v>
+      </c>
+      <c r="K2" t="s">
+        <v>130</v>
+      </c>
+      <c r="L2" s="14">
+        <v>1E-8</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="F3"/>
+      <c r="K3"/>
+      <c r="L3" s="14">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="F4"/>
+      <c r="K4"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="F5"/>
+      <c r="K5"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="F6"/>
+      <c r="K6"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="F7"/>
+      <c r="K7"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="F8"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="F13"/>
+      <c r="K13"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="F31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="F32"/>
+      <c r="K32"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="F33"/>
+      <c r="K33"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="K34"/>
+      <c r="L34"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="F35"/>
+      <c r="K35"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="F36"/>
+      <c r="K36"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="F37"/>
+      <c r="K37"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="F38"/>
+      <c r="K38"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="F39"/>
+      <c r="K39"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="F40"/>
+      <c r="K40"/>
+      <c r="L40"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffin/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF8C550-B507-F442-B289-3D795F529D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F7FF12-A471-C14B-A11E-84FACADDCAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17600" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="148">
   <si>
     <t>Epoch</t>
   </si>
@@ -432,6 +432,57 @@
   </si>
   <si>
     <t>[0.7262 0.4360 0.7171 0.7125 0.6434]</t>
+  </si>
+  <si>
+    <t>[0.7174 0.5061 0.6974 0.6803 0.4724]</t>
+  </si>
+  <si>
+    <t>[0.6568 0.4428 0.6987 0.7385 0.6575]</t>
+  </si>
+  <si>
+    <t>[0.6979 0.4770 0.6871 0.6786 0.4604]</t>
+  </si>
+  <si>
+    <t>[0.7165 0.3945 0.6516 0.4931 0.6243]</t>
+  </si>
+  <si>
+    <t>[0.6987 0.4807 0.6686 0.6579 0.4237]</t>
+  </si>
+  <si>
+    <t>[0.6895 0.4634 0.7029 0.7046 0.5472]</t>
+  </si>
+  <si>
+    <t>[0.6830 0.4699 0.6638 0.6513 0.4009]</t>
+  </si>
+  <si>
+    <t>[0.6534 0.4492 0.6724 0.5948 0.4995]</t>
+  </si>
+  <si>
+    <t>[0.6790 0.4578 0.6564 0.6428 0.3918]</t>
+  </si>
+  <si>
+    <t>[0.6487 0.4806 0.6020 0.6701 0.5475]</t>
+  </si>
+  <si>
+    <t>[0.6956 0.4991 0.6812 0.6719 0.5354]</t>
+  </si>
+  <si>
+    <t>Reset; removed some regularisation (was potentially over-regularising); turned down white noise multiplier to 0.01, halved probability of a fold and changed label smoothing from 0.1 -&gt; 0.05</t>
+  </si>
+  <si>
+    <t>[0.6831 0.3929 0.6924 0.6786 0.7267]</t>
+  </si>
+  <si>
+    <t>[0.6976 0.5066 0.6823 0.6792 0.5690]</t>
+  </si>
+  <si>
+    <t>[0.6883 0.4944 0.7195 0.7207 0.6977]</t>
+  </si>
+  <si>
+    <t>[0.7001 0.5135 0.6984 0.6860 0.5950]</t>
+  </si>
+  <si>
+    <t>[0.6918 0.4906 0.7175 0.7192 0.6922]</t>
   </si>
 </sst>
 </file>
@@ -550,7 +601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -566,7 +617,18 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -574,17 +636,49 @@
   <dxfs count="39">
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
         <name val="Aptos Narrow"/>
         <scheme val="minor"/>
       </font>
@@ -656,48 +750,17 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <scheme val="minor"/>
       </font>
@@ -1123,18 +1186,18 @@
     <tableColumn id="1" xr3:uid="{23378AFE-7605-0143-847E-6BF4D6EC71F7}" name="Epoch" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{8EE2BBDB-2101-934B-B90C-8BC0CA53A271}" name="Train loss" dataDxfId="11"/>
     <tableColumn id="3" xr3:uid="{4BD9BDF7-E421-5845-A339-7F6F4835D46B}" name="Train Accuracy" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{BC399B82-1818-C442-8AF5-A5E6ACD4F9AC}" name="Training Hamming Loss" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{207D034B-40D0-4F4F-BE5B-D77D7E850420}" name="Train Avg F1 Score" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{202B1475-7518-8549-B088-D3B90F6F26B0}" name="Train Label F1 Scores" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{F35ACBEE-D3B4-224E-AE25-FDDB59600115}" name="Val Loss" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{81A115D6-3B37-5F44-B83F-76AC38D42D60}" name="Val Accuracy" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{851DD49C-A36C-C843-AA3A-C3B022F3F8B0}" name="Val Hamming Loss" dataDxfId="0"/>
-    <tableColumn id="8" xr3:uid="{5595516A-7F54-DA48-92BA-0C9BBC2D5E7D}" name="Val Avg F1 Score" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{CD169DB8-5572-8149-B688-EEEDBA4E5E0D}" name="Val Label F1 Scores" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{3AA60CBC-B330-0F40-81AA-8B93624B9AD9}" name="Learning Rate" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{0BF429D1-196F-4B4C-8AC4-789B62E96A73}" name="Notes" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{BC399B82-1818-C442-8AF5-A5E6ACD4F9AC}" name="Training Hamming Loss" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{207D034B-40D0-4F4F-BE5B-D77D7E850420}" name="Train Avg F1 Score" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{202B1475-7518-8549-B088-D3B90F6F26B0}" name="Train Label F1 Scores" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{F35ACBEE-D3B4-224E-AE25-FDDB59600115}" name="Val Loss" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{81A115D6-3B37-5F44-B83F-76AC38D42D60}" name="Val Accuracy" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{851DD49C-A36C-C843-AA3A-C3B022F3F8B0}" name="Val Hamming Loss" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{5595516A-7F54-DA48-92BA-0C9BBC2D5E7D}" name="Val Avg F1 Score" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{CD169DB8-5572-8149-B688-EEEDBA4E5E0D}" name="Val Label F1 Scores" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{3AA60CBC-B330-0F40-81AA-8B93624B9AD9}" name="Learning Rate" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{0BF429D1-196F-4B4C-8AC4-789B62E96A73}" name="Notes" dataDxfId="0"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -3488,10 +3551,10 @@
     <col min="10" max="10" width="16.83203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="31.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="24.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.1640625" style="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3528,11 +3591,11 @@
       <c r="L1" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3569,7 +3632,7 @@
       <c r="L2" s="14">
         <v>1E-8</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="16" t="s">
         <v>129</v>
       </c>
     </row>
@@ -3577,8 +3640,36 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="F3"/>
-      <c r="K3"/>
+      <c r="B3" s="1">
+        <v>0.87760000000000005</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.45619999999999999</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.16850000000000001</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.38169999999999998</v>
+      </c>
+      <c r="F3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.63729999999999998</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.46679999999999999</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.1603</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.39960000000000001</v>
+      </c>
+      <c r="K3" t="s">
+        <v>132</v>
+      </c>
       <c r="L3" s="14">
         <v>2.0000000000000001E-4</v>
       </c>
@@ -3587,69 +3678,270 @@
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="F4"/>
-      <c r="K4"/>
+      <c r="B4" s="1">
+        <v>0.8911</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.43880000000000002</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.17949999999999999</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.37159999999999999</v>
+      </c>
+      <c r="F4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.70109999999999995</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.31840000000000002</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.2334</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.37709999999999999</v>
+      </c>
+      <c r="K4" t="s">
+        <v>134</v>
+      </c>
+      <c r="L4" s="14">
+        <v>4.0000000000000002E-4</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="F5"/>
-      <c r="K5"/>
+      <c r="B5" s="1">
+        <v>0.90629999999999999</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.1908</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.36230000000000001</v>
+      </c>
+      <c r="F5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.65429999999999999</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.49659999999999999</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.1565</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.3674</v>
+      </c>
+      <c r="K5" t="s">
+        <v>136</v>
+      </c>
+      <c r="L5" s="14">
+        <v>5.9999999999999995E-4</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="F6"/>
-      <c r="K6"/>
+      <c r="B6" s="1">
+        <v>0.92030000000000001</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.3926</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.2036</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.35580000000000001</v>
+      </c>
+      <c r="F6" t="s">
+        <v>137</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.6925</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.39050000000000001</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.20019999999999999</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.37440000000000001</v>
+      </c>
+      <c r="K6" t="s">
+        <v>138</v>
+      </c>
+      <c r="L6" s="14">
+        <v>8.0000000000000004E-4</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="F7"/>
-      <c r="K7"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B7" s="1">
+        <v>0.92689999999999995</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.37840000000000001</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.2084</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.35010000000000002</v>
+      </c>
+      <c r="F7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.66979999999999995</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.37519999999999998</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.18640000000000001</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.40029999999999999</v>
+      </c>
+      <c r="K7" t="s">
+        <v>140</v>
+      </c>
+      <c r="L7" s="14">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="F8"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8"/>
+      <c r="B8" s="1">
+        <v>0.77929999999999999</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.47049999999999997</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.1641</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.37059999999999998</v>
+      </c>
+      <c r="F8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.628</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.42799999999999999</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.17419999999999999</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.37590000000000001</v>
+      </c>
+      <c r="K8" t="s">
+        <v>143</v>
+      </c>
+      <c r="L8" s="14">
+        <v>9.7780000000000002E-4</v>
+      </c>
+      <c r="M8" s="18" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9"/>
+      <c r="B9" s="1">
+        <v>0.75819999999999999</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.47939999999999999</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.15709999999999999</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.37630000000000002</v>
+      </c>
+      <c r="F9" t="s">
+        <v>144</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.58550000000000002</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.52829999999999999</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.13539999999999999</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.3947</v>
+      </c>
+      <c r="K9" t="s">
+        <v>145</v>
+      </c>
+      <c r="L9" s="14">
+        <v>8.2200000000000003E-4</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10"/>
+      <c r="B10" s="2">
+        <v>0.75019999999999998</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.48680000000000001</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.15190000000000001</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.38219999999999998</v>
+      </c>
+      <c r="F10" t="s">
+        <v>146</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.56540000000000001</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.5393</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.1343</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.3916</v>
+      </c>
+      <c r="K10" t="s">
+        <v>147</v>
+      </c>
+      <c r="L10" s="14">
+        <v>8.0000000000000004E-4</v>
+      </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
@@ -3665,6 +3957,9 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11"/>
+      <c r="L11" s="14">
+        <v>7.7780000000000004E-4</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
@@ -3680,6 +3975,7 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12"/>
+      <c r="L12" s="14"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
@@ -3687,31 +3983,37 @@
       </c>
       <c r="F13"/>
       <c r="K13"/>
+      <c r="L13" s="14"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
+      <c r="L14" s="14"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
+      <c r="L15" s="14"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
+      <c r="L16" s="14"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
+      <c r="L17" s="14"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
+      <c r="L18" s="14"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
@@ -3724,6 +4026,7 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
+      <c r="L19" s="14"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
@@ -3737,6 +4040,7 @@
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
+      <c r="L20" s="14"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
@@ -3750,6 +4054,7 @@
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
+      <c r="L21" s="14"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
@@ -3763,6 +4068,7 @@
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
+      <c r="L22" s="14"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
@@ -3776,6 +4082,7 @@
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
+      <c r="L23" s="14"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
@@ -3789,11 +4096,13 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
+      <c r="L24" s="14"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
+      <c r="L25" s="14"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
@@ -3804,21 +4113,25 @@
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
+      <c r="L26" s="14"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>26</v>
       </c>
+      <c r="L27" s="14"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>27</v>
       </c>
+      <c r="L28" s="14"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>28</v>
       </c>
+      <c r="L29" s="14"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="1">

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffin/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F7FF12-A471-C14B-A11E-84FACADDCAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1B8901-C5E8-5848-AA1B-61D58B4F7BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17600" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="179">
   <si>
     <t>Epoch</t>
   </si>
@@ -483,6 +483,99 @@
   </si>
   <si>
     <t>[0.6918 0.4906 0.7175 0.7192 0.6922]</t>
+  </si>
+  <si>
+    <t>[0.7045 0.5252 0.6976 0.6989 0.6088]</t>
+  </si>
+  <si>
+    <t>[0.6735 0.4830 0.7192 0.7180 0.6311]</t>
+  </si>
+  <si>
+    <t>[0.7110 0.5144 0.6936 0.6983 0.5780]</t>
+  </si>
+  <si>
+    <t>[0.6767 0.5062 0.7242 0.7271 0.6058]</t>
+  </si>
+  <si>
+    <t>[0.7096 0.5218 0.7059 0.6995 0.6246]</t>
+  </si>
+  <si>
+    <t>[0.6773 0.4927 0.6940 0.6642 0.5487]</t>
+  </si>
+  <si>
+    <t>[0.7035 0.5346 0.6980 0.7023 0.6169]</t>
+  </si>
+  <si>
+    <t>[0.6942 0.4971 0.7175 0.7407 0.6318]</t>
+  </si>
+  <si>
+    <t>[0.7080 0.5251 0.7120 0.7124 0.6302]</t>
+  </si>
+  <si>
+    <t>[0.6074 0.4076 0.7253 0.7005 0.7445]</t>
+  </si>
+  <si>
+    <t>[0.7157 0.5296 0.7090 0.7093 0.6097]</t>
+  </si>
+  <si>
+    <t>[0.7042 0.5373 0.7370 0.7269 0.6947]</t>
+  </si>
+  <si>
+    <t>[0.7192 0.5433 0.7237 0.7177 0.6504]</t>
+  </si>
+  <si>
+    <t>[0.6964 0.5010 0.7179 0.6799 0.5937]</t>
+  </si>
+  <si>
+    <t>[0.7243 0.5494 0.7241 0.7169 0.6423]</t>
+  </si>
+  <si>
+    <t>[0.7120 0.5357 0.7164 0.6933 0.6481]</t>
+  </si>
+  <si>
+    <t>[0.7241 0.5554 0.7269 0.7237 0.6588]</t>
+  </si>
+  <si>
+    <t>[0.7171 0.5250 0.7190 0.7085 0.6034]</t>
+  </si>
+  <si>
+    <t>[0.7233 0.5604 0.7323 0.7314 0.6538]</t>
+  </si>
+  <si>
+    <t>[0.6727 0.4749 0.7229 0.7045 0.6219]</t>
+  </si>
+  <si>
+    <t>[0.7223 0.5500 0.7268 0.7280 0.6469]</t>
+  </si>
+  <si>
+    <t>[0.6571 0.4745 0.7285 0.7334 0.7000]</t>
+  </si>
+  <si>
+    <t>[0.7288 0.5530 0.7425 0.7396 0.6830]</t>
+  </si>
+  <si>
+    <t>[0.6652 0.5160 0.7308 0.7346 0.7446]</t>
+  </si>
+  <si>
+    <t>[0.7053 0.5148 0.7088 0.7077 0.5879]</t>
+  </si>
+  <si>
+    <t>[0.7240 0.5350 0.7431 0.7179 0.6190]</t>
+  </si>
+  <si>
+    <t>[0.7160 0.5313 0.7073 0.7207 0.6242]</t>
+  </si>
+  <si>
+    <t>[0.7347 0.5101 0.7564 0.6907 0.6946]</t>
+  </si>
+  <si>
+    <t>[0.7174 0.5346 0.7117 0.7117 0.6358]</t>
+  </si>
+  <si>
+    <t>[0.7019 0.5160 0.7318 0.6940 0.6397]</t>
+  </si>
+  <si>
+    <t>Reset, add a bit more data augmentation in</t>
   </si>
 </sst>
 </file>
@@ -601,7 +694,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -626,6 +719,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3863,7 +3958,7 @@
       <c r="L8" s="14">
         <v>9.7780000000000002E-4</v>
       </c>
-      <c r="M8" s="18" t="s">
+      <c r="M8" s="16" t="s">
         <v>142</v>
       </c>
     </row>
@@ -3947,16 +4042,36 @@
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11"/>
+      <c r="B11" s="2">
+        <v>0.74609999999999999</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.49390000000000001</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.3841</v>
+      </c>
+      <c r="F11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.5554</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.53120000000000001</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.14169999999999999</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.38840000000000002</v>
+      </c>
+      <c r="K11" t="s">
+        <v>149</v>
+      </c>
       <c r="L11" s="14">
         <v>7.7780000000000004E-4</v>
       </c>
@@ -3965,146 +4080,541 @@
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12"/>
-      <c r="L12" s="14"/>
+      <c r="B12" s="2">
+        <v>0.74760000000000004</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.4919</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.151</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.38379999999999997</v>
+      </c>
+      <c r="F12" t="s">
+        <v>150</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.13139999999999999</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.3695</v>
+      </c>
+      <c r="K12" t="s">
+        <v>151</v>
+      </c>
+      <c r="L12" s="14">
+        <v>7.5560000000000004E-4</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="F13"/>
-      <c r="K13"/>
-      <c r="L13" s="14"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B13" s="1">
+        <v>0.73399999999999999</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.505</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.14380000000000001</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="F13" t="s">
+        <v>152</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0.58509999999999995</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0.47420000000000001</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0.1618</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="K13" t="s">
+        <v>153</v>
+      </c>
+      <c r="L13" s="14">
+        <v>7.3329999999999999E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="L14" s="14"/>
+      <c r="B14" s="1">
+        <v>0.73870000000000002</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.4995</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.1459</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.38740000000000002</v>
+      </c>
+      <c r="F14" t="s">
+        <v>154</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0.56759999999999999</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0.53410000000000002</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0.13220000000000001</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.39340000000000003</v>
+      </c>
+      <c r="K14" t="s">
+        <v>155</v>
+      </c>
+      <c r="L14" s="14">
+        <v>8.4440000000000003E-4</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="L15" s="14"/>
+      <c r="B15" s="1">
+        <v>0.73670000000000002</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.5121</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.1424</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="F15" t="s">
+        <v>156</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0.61860000000000004</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.41520000000000001</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0.17810000000000001</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.38769999999999999</v>
+      </c>
+      <c r="K15" t="s">
+        <v>157</v>
+      </c>
+      <c r="L15" s="14">
+        <v>8.2220000000000004E-4</v>
+      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="L16" s="14"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B16" s="1">
+        <v>0.73719999999999997</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.50970000000000004</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0.39429999999999998</v>
+      </c>
+      <c r="F16" t="s">
+        <v>158</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0.54410000000000003</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0.55810000000000004</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0.1235</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="K16" t="s">
+        <v>159</v>
+      </c>
+      <c r="L16" s="14">
+        <v>8.0000000000000004E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="L17" s="14"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B17" s="1">
+        <v>0.73780000000000001</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.49819999999999998</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.1484</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.3886</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.55859999999999999</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0.5857</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0.1115</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="L17" s="18">
+        <v>7.7780000000000004E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="L18" s="14"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B18" s="1">
+        <v>0.72729999999999995</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.51080000000000003</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0.14030000000000001</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0.39460000000000001</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0.59060000000000001</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0.115</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0.38440000000000002</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="L18" s="14">
+        <v>7.5560000000000004E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="L19" s="14"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B19" s="1">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.51449999999999996</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.13880000000000001</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.39800000000000002</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0.54510000000000003</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0.53269999999999995</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.1348</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0.39710000000000001</v>
+      </c>
+      <c r="K19" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="L19" s="14">
+        <v>7.3329999999999999E-4</v>
+      </c>
+      <c r="M19" s="20" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="L20" s="14"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B20" s="2">
+        <v>0.71389999999999998</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.5292</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.13450000000000001</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.4027</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0.56279999999999997</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0.51349999999999996</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0.13980000000000001</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0.40229999999999999</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="L20" s="14">
+        <v>7.1109999999999999E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="L21" s="14"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B21" s="2">
+        <v>0.71450000000000002</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.53359999999999996</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0.1333</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.40250000000000002</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0.57350000000000001</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0.56430000000000002</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0.1227</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0.39090000000000003</v>
+      </c>
+      <c r="K21" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="L21" s="14">
+        <v>6.667E-4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="L22" s="14"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B22" s="2">
+        <v>0.70679999999999998</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.53869999999999996</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.13089999999999999</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.40820000000000001</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0.54610000000000003</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0.53520000000000001</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0.1336</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0.4017</v>
+      </c>
+      <c r="K22" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="L22" s="14">
+        <v>6.4440000000000005E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="L23" s="14"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B23" s="2">
+        <v>0.70730000000000004</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.53610000000000002</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.13009999999999999</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.40629999999999999</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0.56979999999999997</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0.49940000000000001</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0.40660000000000002</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="L23" s="14">
+        <v>6.2220000000000005E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="L24" s="14"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B24" s="2">
+        <v>0.70430000000000004</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.5353</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0.13070000000000001</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0.40579999999999999</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0.55679999999999996</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0.49390000000000001</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0.1452</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0.41039999999999999</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="L24" s="14">
+        <v>5.9999999999999995E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="L25" s="14"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B25" s="1">
+        <v>0.64929999999999999</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.54390000000000005</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0.12640000000000001</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0.55549999999999999</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0.54079999999999995</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0.12740000000000001</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="L25" s="14">
+        <v>5.7779999999999995E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -4114,31 +4624,34 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="L26" s="14"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="20" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -4146,7 +4659,7 @@
       <c r="K31"/>
       <c r="L31"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>31</v>
       </c>

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffin/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffinfarrow/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1B8901-C5E8-5848-AA1B-61D58B4F7BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64453DD-029F-D945-84CD-90B8E47559A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17600" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
+    <workbookView xWindow="34560" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
   <sheets>
     <sheet name="ResNet" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="181">
   <si>
     <t>Epoch</t>
   </si>
@@ -576,6 +576,12 @@
   </si>
   <si>
     <t>Reset, add a bit more data augmentation in</t>
+  </si>
+  <si>
+    <t>[0.6500 0.4576 0.6232 0.6112 0.4078]</t>
+  </si>
+  <si>
+    <t>[0.6810 0.5139 0.7010 0.7275 0.6550]</t>
   </si>
 </sst>
 </file>
@@ -720,10 +726,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4285,7 +4289,7 @@
       <c r="E17" s="1">
         <v>0.3886</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" t="s">
         <v>172</v>
       </c>
       <c r="G17" s="1">
@@ -4300,7 +4304,7 @@
       <c r="J17" s="1">
         <v>0.39600000000000002</v>
       </c>
-      <c r="K17" s="19" t="s">
+      <c r="K17" t="s">
         <v>173</v>
       </c>
       <c r="L17" s="18">
@@ -4323,7 +4327,7 @@
       <c r="E18" s="1">
         <v>0.39460000000000001</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" t="s">
         <v>174</v>
       </c>
       <c r="G18" s="1">
@@ -4338,7 +4342,7 @@
       <c r="J18" s="1">
         <v>0.38440000000000002</v>
       </c>
-      <c r="K18" s="19" t="s">
+      <c r="K18" t="s">
         <v>175</v>
       </c>
       <c r="L18" s="14">
@@ -4361,7 +4365,7 @@
       <c r="E19" s="2">
         <v>0.39800000000000002</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" t="s">
         <v>176</v>
       </c>
       <c r="G19" s="2">
@@ -4376,13 +4380,13 @@
       <c r="J19" s="2">
         <v>0.39710000000000001</v>
       </c>
-      <c r="K19" s="19" t="s">
+      <c r="K19" t="s">
         <v>177</v>
       </c>
       <c r="L19" s="14">
         <v>7.3329999999999999E-4</v>
       </c>
-      <c r="M19" s="20" t="s">
+      <c r="M19" s="16" t="s">
         <v>61</v>
       </c>
     </row>
@@ -4402,7 +4406,7 @@
       <c r="E20" s="2">
         <v>0.4027</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" t="s">
         <v>160</v>
       </c>
       <c r="G20" s="2">
@@ -4417,11 +4421,11 @@
       <c r="J20" s="2">
         <v>0.40229999999999999</v>
       </c>
-      <c r="K20" s="19" t="s">
+      <c r="K20" t="s">
         <v>161</v>
       </c>
       <c r="L20" s="14">
-        <v>7.1109999999999999E-4</v>
+        <v>7.1120000000000005E-4</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
@@ -4440,7 +4444,7 @@
       <c r="E21" s="2">
         <v>0.40250000000000002</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F21" t="s">
         <v>162</v>
       </c>
       <c r="G21" s="2">
@@ -4455,11 +4459,11 @@
       <c r="J21" s="2">
         <v>0.39090000000000003</v>
       </c>
-      <c r="K21" s="19" t="s">
+      <c r="K21" t="s">
         <v>163</v>
       </c>
       <c r="L21" s="14">
-        <v>6.667E-4</v>
+        <v>6.8900000000000005E-4</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
@@ -4478,7 +4482,7 @@
       <c r="E22" s="2">
         <v>0.40820000000000001</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="F22" t="s">
         <v>164</v>
       </c>
       <c r="G22" s="2">
@@ -4493,11 +4497,11 @@
       <c r="J22" s="2">
         <v>0.4017</v>
       </c>
-      <c r="K22" s="19" t="s">
+      <c r="K22" t="s">
         <v>165</v>
       </c>
-      <c r="L22" s="14">
-        <v>6.4440000000000005E-4</v>
+      <c r="L22" s="18">
+        <v>6.6680000000000005E-4</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
@@ -4516,7 +4520,7 @@
       <c r="E23" s="2">
         <v>0.40629999999999999</v>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F23" t="s">
         <v>166</v>
       </c>
       <c r="G23" s="2">
@@ -4531,11 +4535,11 @@
       <c r="J23" s="2">
         <v>0.40660000000000002</v>
       </c>
-      <c r="K23" s="19" t="s">
+      <c r="K23" t="s">
         <v>167</v>
       </c>
       <c r="L23" s="14">
-        <v>6.2220000000000005E-4</v>
+        <v>6.4459999999999995E-4</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
@@ -4554,7 +4558,7 @@
       <c r="E24" s="2">
         <v>0.40579999999999999</v>
       </c>
-      <c r="F24" s="19" t="s">
+      <c r="F24" t="s">
         <v>168</v>
       </c>
       <c r="G24" s="2">
@@ -4569,11 +4573,11 @@
       <c r="J24" s="2">
         <v>0.41039999999999999</v>
       </c>
-      <c r="K24" s="19" t="s">
+      <c r="K24" t="s">
         <v>169</v>
       </c>
       <c r="L24" s="14">
-        <v>5.9999999999999995E-4</v>
+        <v>6.2239999999999995E-4</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
@@ -4592,7 +4596,7 @@
       <c r="E25" s="1">
         <v>0.41</v>
       </c>
-      <c r="F25" s="19" t="s">
+      <c r="F25" t="s">
         <v>170</v>
       </c>
       <c r="G25" s="1">
@@ -4607,24 +4611,51 @@
       <c r="J25" s="1">
         <v>0.40799999999999997</v>
       </c>
-      <c r="K25" s="19" t="s">
+      <c r="K25" t="s">
         <v>171</v>
       </c>
       <c r="L25" s="14">
-        <v>5.7779999999999995E-4</v>
+        <v>6.0019999999999995E-4</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="20" t="s">
+      <c r="B26" s="1">
+        <v>0.81989999999999996</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0.41339999999999999</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.21149999999999999</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0.35570000000000002</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0.55730000000000002</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0.51959999999999995</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0.13969999999999999</v>
+      </c>
+      <c r="J26" s="19">
+        <v>0.40949999999999998</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="L26" s="14">
+        <v>5.7799999999999995E-4</v>
+      </c>
+      <c r="M26" s="16" t="s">
         <v>178</v>
       </c>
     </row>

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffinfarrow/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64453DD-029F-D945-84CD-90B8E47559A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA08AB8-1BAB-4840-A63D-5297D8CCA70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34560" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="ResNet_Different_Loss" sheetId="3" r:id="rId2"/>
     <sheet name="EfficientNet" sheetId="2" r:id="rId3"/>
     <sheet name="EfficientNet-Retrain" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="183">
   <si>
     <t>Epoch</t>
   </si>
@@ -582,6 +583,12 @@
   </si>
   <si>
     <t>[0.6810 0.5139 0.7010 0.7275 0.6550]</t>
+  </si>
+  <si>
+    <t>[0.6419 0.4860 0.6375 0.6403 0.4302]</t>
+  </si>
+  <si>
+    <t>[0.7142 0.5300 0.7255 0.7125 0.7150]</t>
   </si>
 </sst>
 </file>
@@ -4649,7 +4656,7 @@
       <c r="J26" s="19">
         <v>0.40949999999999998</v>
       </c>
-      <c r="K26" s="20" t="s">
+      <c r="K26" t="s">
         <v>180</v>
       </c>
       <c r="L26" s="14">
@@ -4663,7 +4670,39 @@
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="L27" s="14"/>
+      <c r="B27" s="1">
+        <v>0.80610000000000004</v>
+      </c>
+      <c r="C27" s="1">
+        <v>0.43609999999999999</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0.19750000000000001</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0.36180000000000001</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0.54769999999999996</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0.55159999999999998</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0.1241</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0.41339999999999999</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="L27" s="14">
+        <v>5.3330000000000001E-4</v>
+      </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
@@ -4817,4 +4856,13 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAA60BDE-8BDA-914D-8879-8F477F3344B6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffinfarrow/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA08AB8-1BAB-4840-A63D-5297D8CCA70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F82AD0-3F98-E449-BE2B-5C922E6ADEFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34560" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="185">
   <si>
     <t>Epoch</t>
   </si>
@@ -589,6 +589,12 @@
   </si>
   <si>
     <t>[0.7142 0.5300 0.7255 0.7125 0.7150]</t>
+  </si>
+  <si>
+    <t>[0.6525 0.4962 0.6462 0.6445 0.4238]</t>
+  </si>
+  <si>
+    <t>[0.7137 0.5045 0.7283 0.7289 0.7482]</t>
   </si>
 </sst>
 </file>
@@ -4682,7 +4688,7 @@
       <c r="E27" s="1">
         <v>0.36180000000000001</v>
       </c>
-      <c r="F27" s="20" t="s">
+      <c r="F27" t="s">
         <v>181</v>
       </c>
       <c r="G27" s="1">
@@ -4697,24 +4703,58 @@
       <c r="J27" s="1">
         <v>0.41339999999999999</v>
       </c>
-      <c r="K27" s="20" t="s">
+      <c r="K27" t="s">
         <v>182</v>
       </c>
-      <c r="L27" s="14">
-        <v>5.3330000000000001E-4</v>
+      <c r="L27" s="18">
+        <v>5.5579999999999996E-4</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="L28" s="14"/>
+      <c r="B28" s="1">
+        <v>0.80059999999999998</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0.43790000000000001</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0.19289999999999999</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0.36359999999999998</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0.5383</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0.56210000000000004</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0.1237</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0.39889999999999998</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="L28" s="14">
+        <v>5.3359999999999996E-4</v>
+      </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="L29" s="14"/>
+      <c r="L29" s="14">
+        <v>5.1139999999999996E-4</v>
+      </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="1">

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffinfarrow/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F82AD0-3F98-E449-BE2B-5C922E6ADEFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77BB177-8856-DA44-A4B8-E6125463EC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
+    <workbookView xWindow="34560" yWindow="500" windowWidth="38400" windowHeight="19660" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
   <sheets>
     <sheet name="ResNet" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="187">
   <si>
     <t>Epoch</t>
   </si>
@@ -595,6 +595,12 @@
   </si>
   <si>
     <t>[0.7137 0.5045 0.7283 0.7289 0.7482]</t>
+  </si>
+  <si>
+    <t>[0.6648 0.5068 0.6553 0.6573 0.4868]</t>
+  </si>
+  <si>
+    <t>[0.7159 0.5593 0.7215 0.7169 0.6808]</t>
   </si>
 </sst>
 </file>
@@ -4726,7 +4732,7 @@
       <c r="E28" s="1">
         <v>0.36359999999999998</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="F28" t="s">
         <v>183</v>
       </c>
       <c r="G28" s="1">
@@ -4741,7 +4747,7 @@
       <c r="J28" s="1">
         <v>0.39889999999999998</v>
       </c>
-      <c r="K28" s="20" t="s">
+      <c r="K28" t="s">
         <v>184</v>
       </c>
       <c r="L28" s="14">
@@ -4752,6 +4758,36 @@
       <c r="A29" s="1">
         <v>28</v>
       </c>
+      <c r="B29" s="1">
+        <v>0.78910000000000002</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0.45519999999999999</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0.1812</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0.5423</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0.56640000000000001</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0.40560000000000002</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>186</v>
+      </c>
       <c r="L29" s="14">
         <v>5.1139999999999996E-4</v>
       </c>
@@ -4759,6 +4795,9 @@
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>29</v>
+      </c>
+      <c r="L30" s="14">
+        <v>4.8890000000000001E-4</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffinfarrow/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77BB177-8856-DA44-A4B8-E6125463EC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D6FFC7-80D7-2A49-8611-19105B8449F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34560" yWindow="500" windowWidth="38400" windowHeight="19660" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="189">
   <si>
     <t>Epoch</t>
   </si>
@@ -601,6 +601,12 @@
   </si>
   <si>
     <t>[0.7159 0.5593 0.7215 0.7169 0.6808]</t>
+  </si>
+  <si>
+    <t>[0.6698 0.5001 0.6440 0.6564 0.4560]</t>
+  </si>
+  <si>
+    <t>[0.7204 0.5095 0.7396 0.7269 0.7295]</t>
   </si>
 </sst>
 </file>
@@ -4770,7 +4776,7 @@
       <c r="E29" s="1">
         <v>0.37</v>
       </c>
-      <c r="F29" s="20" t="s">
+      <c r="F29" t="s">
         <v>185</v>
       </c>
       <c r="G29" s="1">
@@ -4785,7 +4791,7 @@
       <c r="J29" s="1">
         <v>0.40560000000000002</v>
       </c>
-      <c r="K29" s="20" t="s">
+      <c r="K29" t="s">
         <v>186</v>
       </c>
       <c r="L29" s="14">
@@ -4796,6 +4802,36 @@
       <c r="A30" s="1">
         <v>29</v>
       </c>
+      <c r="B30" s="1">
+        <v>0.7944</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0.45119999999999999</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0.18329999999999999</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0.36780000000000002</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0.54369999999999996</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0.57569999999999999</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0.1173</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0.40210000000000001</v>
+      </c>
+      <c r="K30" s="20" t="s">
+        <v>188</v>
+      </c>
       <c r="L30" s="14">
         <v>4.8890000000000001E-4</v>
       </c>
@@ -4806,7 +4842,9 @@
       </c>
       <c r="F31"/>
       <c r="K31"/>
-      <c r="L31"/>
+      <c r="L31" s="18">
+        <v>4.6670000000000001E-4</v>
+      </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="1">

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffinfarrow/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D6FFC7-80D7-2A49-8611-19105B8449F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3075F5E-F55E-1249-8AE6-C1069C2A25BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34560" yWindow="500" windowWidth="38400" windowHeight="19660" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="191">
   <si>
     <t>Epoch</t>
   </si>
@@ -607,6 +607,12 @@
   </si>
   <si>
     <t>[0.7204 0.5095 0.7396 0.7269 0.7295]</t>
+  </si>
+  <si>
+    <t>[0.6730 0.5070 0.6595 0.6647 0.4636]</t>
+  </si>
+  <si>
+    <t>[0.7089 0.5134 0.7341 0.7108 0.6278]</t>
   </si>
 </sst>
 </file>
@@ -725,7 +731,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -752,7 +758,6 @@
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4814,7 +4819,7 @@
       <c r="E30" s="1">
         <v>0.36780000000000002</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="F30" t="s">
         <v>187</v>
       </c>
       <c r="G30" s="1">
@@ -4829,7 +4834,7 @@
       <c r="J30" s="1">
         <v>0.40210000000000001</v>
       </c>
-      <c r="K30" s="20" t="s">
+      <c r="K30" t="s">
         <v>188</v>
       </c>
       <c r="L30" s="14">
@@ -4840,8 +4845,36 @@
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="F31"/>
-      <c r="K31"/>
+      <c r="B31" s="1">
+        <v>0.78459999999999996</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0.4607</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0.17860000000000001</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0.37080000000000002</v>
+      </c>
+      <c r="F31" t="s">
+        <v>189</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0.55720000000000003</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0.5423</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0.12839999999999999</v>
+      </c>
+      <c r="J31" s="1">
+        <v>0.41060000000000002</v>
+      </c>
+      <c r="K31" t="s">
+        <v>190</v>
+      </c>
       <c r="L31" s="18">
         <v>4.6670000000000001E-4</v>
       </c>
@@ -4852,6 +4885,9 @@
       </c>
       <c r="F32"/>
       <c r="K32"/>
+      <c r="L32" s="14">
+        <v>4.4440000000000001E-4</v>
+      </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="1">

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffinfarrow/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffin/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D6FFC7-80D7-2A49-8611-19105B8449F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E738C70-B7DD-8E49-B44E-C5ED684558EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="500" windowWidth="38400" windowHeight="19660" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17600" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
   <sheets>
     <sheet name="ResNet" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="191">
   <si>
     <t>Epoch</t>
   </si>
@@ -607,6 +607,12 @@
   </si>
   <si>
     <t>[0.7204 0.5095 0.7396 0.7269 0.7295]</t>
+  </si>
+  <si>
+    <t>[0.6730 0.5070 0.6595 0.6647 0.4636]</t>
+  </si>
+  <si>
+    <t>[0.7089 0.5134 0.7341 0.7108 0.6278]</t>
   </si>
 </sst>
 </file>
@@ -725,7 +731,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -752,7 +758,6 @@
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4814,7 +4819,7 @@
       <c r="E30" s="1">
         <v>0.36780000000000002</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="F30" t="s">
         <v>187</v>
       </c>
       <c r="G30" s="1">
@@ -4829,7 +4834,7 @@
       <c r="J30" s="1">
         <v>0.40210000000000001</v>
       </c>
-      <c r="K30" s="20" t="s">
+      <c r="K30" t="s">
         <v>188</v>
       </c>
       <c r="L30" s="14">
@@ -4840,8 +4845,36 @@
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="F31"/>
-      <c r="K31"/>
+      <c r="B31" s="1">
+        <v>0.78459999999999996</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0.4607</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0.17860000000000001</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0.37080000000000002</v>
+      </c>
+      <c r="F31" t="s">
+        <v>189</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0.55720000000000003</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0.5423</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0.12839999999999999</v>
+      </c>
+      <c r="J31" s="1">
+        <v>0.41060000000000002</v>
+      </c>
+      <c r="K31" t="s">
+        <v>190</v>
+      </c>
       <c r="L31" s="18">
         <v>4.6670000000000001E-4</v>
       </c>

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffinfarrow/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffin/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3075F5E-F55E-1249-8AE6-C1069C2A25BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258941ED-28DB-D542-9286-1154F6CF04A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="500" windowWidth="38400" windowHeight="19660" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17600" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
   <sheets>
     <sheet name="ResNet" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="204">
   <si>
     <t>Epoch</t>
   </si>
@@ -613,6 +613,45 @@
   </si>
   <si>
     <t>[0.7089 0.5134 0.7341 0.7108 0.6278]</t>
+  </si>
+  <si>
+    <t>[0.7266 0.5642 0.7267 0.7253 0.6550]</t>
+  </si>
+  <si>
+    <t>]</t>
+  </si>
+  <si>
+    <t>[0.7025 0.5423 0.7430 0.7169 0.6122]</t>
+  </si>
+  <si>
+    <t>[0.7264 0.5688 0.7314 0.7391 0.6925]</t>
+  </si>
+  <si>
+    <t>[0.6763 0.5186 0.7500 0.7145 0.5760]</t>
+  </si>
+  <si>
+    <t>[0.7316 0.5808 0.7380 0.7460 0.6964]</t>
+  </si>
+  <si>
+    <t>[0.7202 0.5223 0.7463 0.6849 0.6693]</t>
+  </si>
+  <si>
+    <t>[0.7386 0.5737 0.7500 0.7427 0.6714]</t>
+  </si>
+  <si>
+    <t>[0.7205 0.5440 0.7110 0.7168 0.7118</t>
+  </si>
+  <si>
+    <t>[0.7383 0.5939 0.7516 0.7609 0.7075]</t>
+  </si>
+  <si>
+    <t>[0.6936 0.5317 0.7538 0.7341 0.7643]</t>
+  </si>
+  <si>
+    <t>[0.7381 0.5920 0.7513 0.7529 0.7258]</t>
+  </si>
+  <si>
+    <t>[0.7202 0.5928 0.7653 0.7115 0.7382]</t>
   </si>
 </sst>
 </file>
@@ -731,7 +770,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -758,6 +797,9 @@
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4879,59 +4921,243 @@
         <v>4.6670000000000001E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="F32"/>
-      <c r="K32"/>
+      <c r="B32" s="1">
+        <v>0.70169999999999999</v>
+      </c>
+      <c r="C32" s="1">
+        <v>0.53820000000000001</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0.1288</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0.40689999999999998</v>
+      </c>
+      <c r="F32" t="s">
+        <v>191</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0.54720000000000002</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0.57440000000000002</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0.12039999999999999</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0.41039999999999999</v>
+      </c>
+      <c r="K32" t="s">
+        <v>193</v>
+      </c>
       <c r="L32" s="14">
         <v>4.4440000000000001E-4</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="F33"/>
-      <c r="K33"/>
+      <c r="B33" s="1">
+        <v>0.69230000000000003</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0.5514</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0.12540000000000001</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0.41239999999999999</v>
+      </c>
+      <c r="F33" t="s">
+        <v>194</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0.54237999999999997</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0.55149999999999999</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0.1275</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0.39739999999999998</v>
+      </c>
+      <c r="K33" t="s">
+        <v>195</v>
+      </c>
+      <c r="L33" s="14">
+        <v>4.2220000000000002E-4</v>
+      </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="F34"/>
-      <c r="G34"/>
-      <c r="K34"/>
-      <c r="L34"/>
+      <c r="B34" s="1">
+        <v>0.68310000000000004</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0.56020000000000003</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0.1202</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0.41589999999999999</v>
+      </c>
+      <c r="F34" t="s">
+        <v>196</v>
+      </c>
+      <c r="G34">
+        <v>0.54220000000000002</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0.5403</v>
+      </c>
+      <c r="I34" s="1">
+        <v>0.125</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0.42059999999999997</v>
+      </c>
+      <c r="K34" t="s">
+        <v>197</v>
+      </c>
+      <c r="L34" s="18">
+        <v>4.0000000000000002E-4</v>
+      </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="F35"/>
-      <c r="K35"/>
+      <c r="B35" s="1">
+        <v>0.67969999999999997</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.56130000000000002</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0.1196</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0.41710000000000003</v>
+      </c>
+      <c r="F35" t="s">
+        <v>198</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.53690000000000004</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0.55520000000000003</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0.1221</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0.41770000000000002</v>
+      </c>
+      <c r="K35" t="s">
+        <v>199</v>
+      </c>
+      <c r="L35" s="14">
+        <v>3.7780000000000002E-4</v>
+      </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="F36"/>
-      <c r="K36"/>
+      <c r="B36" s="1">
+        <v>0.67110000000000003</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.57530000000000003</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.1145</v>
+      </c>
+      <c r="E36" s="1">
+        <v>0.42309999999999998</v>
+      </c>
+      <c r="F36" t="s">
+        <v>200</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0.52890000000000004</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0.56930000000000003</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0.1188</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0.41720000000000002</v>
+      </c>
+      <c r="K36" t="s">
+        <v>201</v>
+      </c>
+      <c r="L36" s="14">
+        <v>3.5560000000000002E-4</v>
+      </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="F37"/>
-      <c r="K37"/>
+      <c r="B37" s="1">
+        <v>0.67020000000000002</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0.57709999999999995</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0.1147</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0.42349999999999999</v>
+      </c>
+      <c r="F37" t="s">
+        <v>202</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.53879999999999995</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0.5958</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0.1082</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0.41620000000000001</v>
+      </c>
+      <c r="K37" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="F38"/>
+      <c r="F38" t="s">
+        <v>192</v>
+      </c>
       <c r="K38"/>
+      <c r="L38" s="14"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
@@ -4939,6 +5165,7 @@
       </c>
       <c r="F39"/>
       <c r="K39"/>
+      <c r="L39" s="14"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
@@ -4946,27 +5173,31 @@
       </c>
       <c r="F40"/>
       <c r="K40"/>
-      <c r="L40"/>
+      <c r="L40" s="14"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>40</v>
       </c>
+      <c r="L41" s="14"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>41</v>
       </c>
+      <c r="L42" s="14"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>42</v>
       </c>
+      <c r="L43" s="14"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>43</v>
       </c>
+      <c r="L44" s="14"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="1">

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffin/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258941ED-28DB-D542-9286-1154F6CF04A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410A5143-677E-CF48-876B-B004B5343769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17600" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="203">
   <si>
     <t>Epoch</t>
   </si>
@@ -616,9 +616,6 @@
   </si>
   <si>
     <t>[0.7266 0.5642 0.7267 0.7253 0.6550]</t>
-  </si>
-  <si>
-    <t>]</t>
   </si>
   <si>
     <t>[0.7025 0.5423 0.7430 0.7169 0.6122]</t>
@@ -4953,7 +4950,7 @@
         <v>0.41039999999999999</v>
       </c>
       <c r="K32" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L32" s="14">
         <v>4.4440000000000001E-4</v>
@@ -4979,7 +4976,7 @@
         <v>0.41239999999999999</v>
       </c>
       <c r="F33" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G33" s="1">
         <v>0.54237999999999997</v>
@@ -4994,7 +4991,7 @@
         <v>0.39739999999999998</v>
       </c>
       <c r="K33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L33" s="14">
         <v>4.2220000000000002E-4</v>
@@ -5017,7 +5014,7 @@
         <v>0.41589999999999999</v>
       </c>
       <c r="F34" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G34">
         <v>0.54220000000000002</v>
@@ -5032,7 +5029,7 @@
         <v>0.42059999999999997</v>
       </c>
       <c r="K34" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L34" s="18">
         <v>4.0000000000000002E-4</v>
@@ -5055,7 +5052,7 @@
         <v>0.41710000000000003</v>
       </c>
       <c r="F35" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G35" s="1">
         <v>0.53690000000000004</v>
@@ -5070,7 +5067,7 @@
         <v>0.41770000000000002</v>
       </c>
       <c r="K35" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L35" s="14">
         <v>3.7780000000000002E-4</v>
@@ -5093,7 +5090,7 @@
         <v>0.42309999999999998</v>
       </c>
       <c r="F36" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G36" s="1">
         <v>0.52890000000000004</v>
@@ -5108,7 +5105,7 @@
         <v>0.41720000000000002</v>
       </c>
       <c r="K36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L36" s="14">
         <v>3.5560000000000002E-4</v>
@@ -5131,7 +5128,7 @@
         <v>0.42349999999999999</v>
       </c>
       <c r="F37" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G37" s="1">
         <v>0.53879999999999995</v>
@@ -5146,18 +5143,21 @@
         <v>0.41620000000000001</v>
       </c>
       <c r="K37" t="s">
-        <v>203</v>
+        <v>202</v>
+      </c>
+      <c r="L37" s="14">
+        <v>3.3340000000000003E-4</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="F38" t="s">
-        <v>192</v>
-      </c>
+      <c r="F38"/>
       <c r="K38"/>
-      <c r="L38" s="14"/>
+      <c r="L38" s="14">
+        <v>3.1119999999999997E-4</v>
+      </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
@@ -5165,7 +5165,9 @@
       </c>
       <c r="F39"/>
       <c r="K39"/>
-      <c r="L39" s="14"/>
+      <c r="L39" s="18">
+        <v>2.8899999999999998E-4</v>
+      </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
@@ -5173,65 +5175,96 @@
       </c>
       <c r="F40"/>
       <c r="K40"/>
-      <c r="L40" s="14"/>
+      <c r="L40" s="14">
+        <v>2.6679999999999998E-4</v>
+      </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="L41" s="14"/>
+      <c r="L41" s="14">
+        <v>2.4459999999999998E-4</v>
+      </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="L42" s="14"/>
+      <c r="L42" s="14">
+        <v>2.2240000000000001E-4</v>
+      </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="L43" s="14"/>
+      <c r="L43" s="14">
+        <v>2.0019999999999999E-4</v>
+      </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="L44" s="14"/>
+      <c r="L44" s="18">
+        <v>1.7799999999999999E-4</v>
+      </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>44</v>
       </c>
+      <c r="L45" s="14">
+        <v>1.5579999999999999E-4</v>
+      </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>45</v>
       </c>
+      <c r="L46" s="14">
+        <v>1.3359999999999999E-4</v>
+      </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>46</v>
       </c>
+      <c r="L47" s="14">
+        <v>1.114E-4</v>
+      </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="L48" s="14">
+        <v>8.92E-5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="L49" s="18">
+        <v>6.7000000000000002E-5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="L50" s="14">
+        <v>4.4799999999999998E-5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>50</v>
+      </c>
+      <c r="L51" s="14">
+        <v>2.26E-5</v>
       </c>
     </row>
   </sheetData>

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffin/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410A5143-677E-CF48-876B-B004B5343769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04F65D3-0B87-164D-BFD6-71D749AC06EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17600" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="215">
   <si>
     <t>Epoch</t>
   </si>
@@ -649,6 +649,42 @@
   </si>
   <si>
     <t>[0.7202 0.5928 0.7653 0.7115 0.7382]</t>
+  </si>
+  <si>
+    <t>[0.7340 0.5962 0.7565 0.7654 0.7172]</t>
+  </si>
+  <si>
+    <t>[0.7145 0.5228 0.7362 0.7289 0.7275]</t>
+  </si>
+  <si>
+    <t>[0.7380 0.6010 0.7552 0.7636 0.7144]</t>
+  </si>
+  <si>
+    <t>[0.7127 0.5170 0.7379 0.7056 0.6857]</t>
+  </si>
+  <si>
+    <t>[0.7365 0.6155 0.7709 0.7647 0.7265]</t>
+  </si>
+  <si>
+    <t>[0.7185 0.5185 0.7443 0.6959 0.7045]</t>
+  </si>
+  <si>
+    <t>[0.7461 0.6161 0.7750 0.7700 0.7307]</t>
+  </si>
+  <si>
+    <t>[0.7279 0.4968 0.7511 0.6965 0.6973]</t>
+  </si>
+  <si>
+    <t>[0.7510 0.6227 0.7748 0.7802 0.7263]</t>
+  </si>
+  <si>
+    <t>[0.7159 0.5234 0.7462 0.7116 0.7341]</t>
+  </si>
+  <si>
+    <t>[0.7554 0.6354 0.7773 0.7858 0.7339]</t>
+  </si>
+  <si>
+    <t>[0.7270 0.4998 0.7487 0.7155 0.7852]</t>
   </si>
 </sst>
 </file>
@@ -794,9 +830,7 @@
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4955,11 +4989,11 @@
       <c r="L32" s="14">
         <v>4.4440000000000001E-4</v>
       </c>
-      <c r="M32" s="20" t="s">
+      <c r="M32" s="16" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -4997,7 +5031,7 @@
         <v>4.2220000000000002E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -5035,7 +5069,7 @@
         <v>4.0000000000000002E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -5073,7 +5107,7 @@
         <v>3.7780000000000002E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -5111,7 +5145,7 @@
         <v>3.5560000000000002E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5149,61 +5183,238 @@
         <v>3.3340000000000003E-4</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="F38"/>
-      <c r="K38"/>
+      <c r="B38" s="1">
+        <v>0.66510000000000002</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0.5776</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0.1129</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0.42580000000000001</v>
+      </c>
+      <c r="F38" t="s">
+        <v>203</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0.54810000000000003</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0.1196</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0.4163</v>
+      </c>
+      <c r="K38" t="s">
+        <v>204</v>
+      </c>
       <c r="L38" s="14">
         <v>3.1119999999999997E-4</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="F39"/>
-      <c r="K39"/>
+      <c r="B39" s="1">
+        <v>0.65939999999999999</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.58260000000000001</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0.111</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0.42509999999999998</v>
+      </c>
+      <c r="F39" t="s">
+        <v>205</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.54479999999999995</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0.55889999999999995</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0.1229</v>
+      </c>
+      <c r="J39" s="1">
+        <v>0.40620000000000001</v>
+      </c>
+      <c r="K39" t="s">
+        <v>206</v>
+      </c>
       <c r="L39" s="18">
         <v>2.8899999999999998E-4</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="F40"/>
-      <c r="K40"/>
+      <c r="B40" s="1">
+        <v>0.65149999999999997</v>
+      </c>
+      <c r="C40" s="1">
+        <v>0.59809999999999997</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0.1076</v>
+      </c>
+      <c r="E40" s="1">
+        <v>0.43190000000000001</v>
+      </c>
+      <c r="F40" t="s">
+        <v>207</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0.54969999999999997</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0.53010000000000002</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0.1285</v>
+      </c>
+      <c r="J40" s="1">
+        <v>0.4163</v>
+      </c>
+      <c r="K40" t="s">
+        <v>208</v>
+      </c>
       <c r="L40" s="14">
         <v>2.6679999999999998E-4</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>40</v>
       </c>
+      <c r="B41" s="1">
+        <v>0.64710000000000001</v>
+      </c>
+      <c r="C41" s="1">
+        <v>0.60109999999999997</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0.1048</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0.43430000000000002</v>
+      </c>
+      <c r="F41" t="s">
+        <v>209</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0.53969999999999996</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0.5514</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0.1235</v>
+      </c>
+      <c r="J41" s="1">
+        <v>0.40949999999999998</v>
+      </c>
+      <c r="K41" t="s">
+        <v>210</v>
+      </c>
       <c r="L41" s="14">
         <v>2.4459999999999998E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>41</v>
       </c>
+      <c r="B42" s="1">
+        <v>0.65010000000000001</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.60860000000000003</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0.1021</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0.43709999999999999</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.53879999999999995</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0.56230000000000002</v>
+      </c>
+      <c r="I42" s="1">
+        <v>0.1192</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0.41970000000000002</v>
+      </c>
+      <c r="K42" s="20" t="s">
+        <v>212</v>
+      </c>
       <c r="L42" s="14">
         <v>2.2240000000000001E-4</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>42</v>
       </c>
+      <c r="B43" s="1">
+        <v>0.63739999999999997</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0.61529999999999996</v>
+      </c>
+      <c r="D43" s="1">
+        <v>9.9400000000000002E-2</v>
+      </c>
+      <c r="E43" s="1">
+        <v>0.4395</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0.54310000000000003</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0.5484</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0.1244</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0.41909999999999997</v>
+      </c>
+      <c r="K43" s="20" t="s">
+        <v>214</v>
+      </c>
       <c r="L43" s="14">
         <v>2.0019999999999999E-4</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -5211,7 +5422,7 @@
         <v>1.7799999999999999E-4</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -5219,7 +5430,7 @@
         <v>1.5579999999999999E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -5227,7 +5438,7 @@
         <v>1.3359999999999999E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -5235,7 +5446,7 @@
         <v>1.114E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>47</v>
       </c>

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffin/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffinfarrow/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04F65D3-0B87-164D-BFD6-71D749AC06EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F003253-0E4D-7542-90E6-56686D6799F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17600" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20060" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
   <sheets>
     <sheet name="ResNet" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="EfficientNet-Retrain" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="252">
   <si>
     <t>Epoch</t>
   </si>
@@ -685,6 +685,117 @@
   </si>
   <si>
     <t>[0.7270 0.4998 0.7487 0.7155 0.7852]</t>
+  </si>
+  <si>
+    <t>Reset, removed some data augmentation (we are possibly *over* augmenting), changing learning rate scheduler to be cyclical --&gt; worth exploring increasing the learning rate to escape a local minimum?</t>
+  </si>
+  <si>
+    <t>[0.7732 0.6668 0.8271 0.8226 0.7903]</t>
+  </si>
+  <si>
+    <t>[0.7124 0.5098 0.7614 0.7101 0.8131]</t>
+  </si>
+  <si>
+    <t>[0.7754 0.7021 0.8361 0.8361 0.8120]</t>
+  </si>
+  <si>
+    <t>[0.7256 0.5537 0.7509 0.6891 0.8287]</t>
+  </si>
+  <si>
+    <t>[0.7794 0.7173 0.8394 0.8397 0.8052]</t>
+  </si>
+  <si>
+    <t>[0.7270 0.5509 0.7411 0.7072 0.8510]</t>
+  </si>
+  <si>
+    <t>[0.7995 0.7165 0.8418 0.8396 0.8171]</t>
+  </si>
+  <si>
+    <t>[0.7214 0.5477 0.7401 0.7003 0.8125]</t>
+  </si>
+  <si>
+    <t>[0.7947 0.7122 0.8493 0.8450 0.7718]</t>
+  </si>
+  <si>
+    <t>[0.7309 0.5076 0.7165 0.6900 0.8235]</t>
+  </si>
+  <si>
+    <t>[0.8020 0.7425 0.8626 0.8458 0.8002]</t>
+  </si>
+  <si>
+    <t>[0.6975 0.5125 0.7267 0.6970 0.7893]</t>
+  </si>
+  <si>
+    <t>reset, adding in significantly more augmentation</t>
+  </si>
+  <si>
+    <t>[0.6860 0.5231 0.6958 0.6904 0.4044]</t>
+  </si>
+  <si>
+    <t>[0.7139 0.4733 0.7140 0.6733 0.7757]</t>
+  </si>
+  <si>
+    <t>[0.7063 0.5422 0.7210 0.7222 0.4175]</t>
+  </si>
+  <si>
+    <t>[0.7124 0.5585 0.7326 0.7234 0.4293]</t>
+  </si>
+  <si>
+    <t>[0.7215 0.5425 0.7271 0.7005 0.7987]</t>
+  </si>
+  <si>
+    <t>[0.7175 0.5669 0.7355 0.7308 0.4283]</t>
+  </si>
+  <si>
+    <t>[0.7267 0.4988 0.7338 0.7115 0.7496]</t>
+  </si>
+  <si>
+    <t>[0.7114 0.5690 0.7385 0.7198 0.4291]</t>
+  </si>
+  <si>
+    <t>[0.7292 0.5122 0.7247 0.7340 0.7330]</t>
+  </si>
+  <si>
+    <t>[0.7128 0.5825 0.7328 0.7300 0.4254]</t>
+  </si>
+  <si>
+    <t>[0.7297 0.4997 0.7291 0.6967 0.8110]</t>
+  </si>
+  <si>
+    <t>[0.7044 0.5591 0.7197 0.7067 0.4242]</t>
+  </si>
+  <si>
+    <t>[0.7200 0.4886 0.7186 0.7127 0.6729]</t>
+  </si>
+  <si>
+    <t>[0.7119 0.5475 0.7273 0.7151 0.4382]</t>
+  </si>
+  <si>
+    <t>[0.7438 0.5345 0.7233 0.7005 0.7178]</t>
+  </si>
+  <si>
+    <t>[0.7087 0.5636 0.7310 0.7149 0.4287]</t>
+  </si>
+  <si>
+    <t>[0.7333 0.4851 0.7280 0.6683 0.7690]</t>
+  </si>
+  <si>
+    <t>[0.7194 0.5708 0.7377 0.7276 0.4370]</t>
+  </si>
+  <si>
+    <t>[0.7284 0.4857 0.7311 0.6843 0.7501]</t>
+  </si>
+  <si>
+    <t>[0.7196 0.5868 0.7485 0.7435 0.4498]</t>
+  </si>
+  <si>
+    <t>[0.7581 0.5482 0.7205 0.7178 0.7846]</t>
+  </si>
+  <si>
+    <t>[0.7251 0.5924 0.7572 0.7430 0.4660]</t>
+  </si>
+  <si>
+    <t>[0.7202 0.5434 0.7336 0.7123 0.6815]</t>
   </si>
 </sst>
 </file>
@@ -803,7 +914,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -831,6 +942,9 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3740,7 +3854,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{792EDA06-FC2C-024C-AE8E-C1CCD07C3F11}">
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5" style="1" customWidth="1"/>
@@ -5354,7 +5468,7 @@
       <c r="E42" s="1">
         <v>0.43709999999999999</v>
       </c>
-      <c r="F42" s="20" t="s">
+      <c r="F42" t="s">
         <v>211</v>
       </c>
       <c r="G42" s="1">
@@ -5369,7 +5483,7 @@
       <c r="J42" s="1">
         <v>0.41970000000000002</v>
       </c>
-      <c r="K42" s="20" t="s">
+      <c r="K42" t="s">
         <v>212</v>
       </c>
       <c r="L42" s="14">
@@ -5392,7 +5506,7 @@
       <c r="E43" s="1">
         <v>0.4395</v>
       </c>
-      <c r="F43" s="20" t="s">
+      <c r="F43" t="s">
         <v>213</v>
       </c>
       <c r="G43" s="1">
@@ -5407,75 +5521,716 @@
       <c r="J43" s="1">
         <v>0.41909999999999997</v>
       </c>
-      <c r="K43" s="20" t="s">
+      <c r="K43" t="s">
         <v>214</v>
       </c>
       <c r="L43" s="14">
         <v>2.0019999999999999E-4</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>43</v>
       </c>
+      <c r="B44" s="1">
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="C44" s="1">
+        <v>0.67049999999999998</v>
+      </c>
+      <c r="D44" s="1">
+        <v>8.1299999999999997E-2</v>
+      </c>
+      <c r="E44" s="1">
+        <v>0.46210000000000001</v>
+      </c>
+      <c r="F44" t="s">
+        <v>216</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0.55489999999999995</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0.55920000000000003</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0.12280000000000001</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0.4078</v>
+      </c>
+      <c r="K44" t="s">
+        <v>217</v>
+      </c>
       <c r="L44" s="18">
         <v>1.7799999999999999E-4</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>44</v>
       </c>
+      <c r="B45" s="1">
+        <v>0.57830000000000004</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0.69059999999999999</v>
+      </c>
+      <c r="D45" s="1">
+        <v>7.5200000000000003E-2</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0.46739999999999998</v>
+      </c>
+      <c r="F45" t="s">
+        <v>218</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0.55689999999999995</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0.56759999999999999</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0.1148</v>
+      </c>
+      <c r="J45" s="1">
+        <v>0.41339999999999999</v>
+      </c>
+      <c r="K45" t="s">
+        <v>219</v>
+      </c>
       <c r="L45" s="14">
-        <v>1.5579999999999999E-4</v>
+        <v>1.7780000000000001E-4</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>45</v>
       </c>
+      <c r="B46" s="1">
+        <v>0.57489999999999997</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0.69469999999999998</v>
+      </c>
+      <c r="D46" s="1">
+        <v>7.3300000000000004E-2</v>
+      </c>
+      <c r="E46" s="1">
+        <v>0.47020000000000001</v>
+      </c>
+      <c r="F46" t="s">
+        <v>220</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0.56140000000000001</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0.58130000000000004</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0.1137</v>
+      </c>
+      <c r="J46" s="1">
+        <v>0.41639999999999999</v>
+      </c>
+      <c r="K46" t="s">
+        <v>221</v>
+      </c>
       <c r="L46" s="14">
-        <v>1.3359999999999999E-4</v>
+        <v>2.2159999999999999E-4</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>46</v>
       </c>
+      <c r="B47" s="1">
+        <v>0.57110000000000005</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.70620000000000005</v>
+      </c>
+      <c r="D47" s="1">
+        <v>7.0599999999999996E-2</v>
+      </c>
+      <c r="E47" s="1">
+        <v>0.47310000000000002</v>
+      </c>
+      <c r="F47" t="s">
+        <v>222</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0.57020000000000004</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0.57269999999999999</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0.1178</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0.4113</v>
+      </c>
+      <c r="K47" t="s">
+        <v>223</v>
+      </c>
       <c r="L47" s="14">
-        <v>1.114E-4</v>
+        <v>2.6400000000000002E-4</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>47</v>
       </c>
+      <c r="B48" s="1">
+        <v>0.56759999999999999</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="D48" s="1">
+        <v>7.0900000000000005E-2</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="F48" t="s">
+        <v>224</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0.59819999999999995</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0.53049999999999997</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0.12939999999999999</v>
+      </c>
+      <c r="J48" s="1">
+        <v>0.40970000000000001</v>
+      </c>
+      <c r="K48" t="s">
+        <v>225</v>
+      </c>
       <c r="L48" s="14">
-        <v>8.92E-5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3.0479999999999998E-4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>48</v>
       </c>
+      <c r="B49" s="1">
+        <v>0.55510000000000004</v>
+      </c>
+      <c r="C49" s="1">
+        <v>0.72870000000000001</v>
+      </c>
+      <c r="D49" s="1">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0.48159999999999997</v>
+      </c>
+      <c r="F49" t="s">
+        <v>226</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0.59130000000000005</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0.55830000000000002</v>
+      </c>
+      <c r="I49" s="1">
+        <v>0.1232</v>
+      </c>
+      <c r="J49" s="1">
+        <v>0.39639999999999997</v>
+      </c>
+      <c r="K49" t="s">
+        <v>227</v>
+      </c>
       <c r="L49" s="18">
-        <v>6.7000000000000002E-5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+        <v>2.8079999999999999E-4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>49</v>
       </c>
+      <c r="B50" s="1">
+        <v>0.87360000000000004</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0.48089999999999999</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0.1817</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0.3987</v>
+      </c>
+      <c r="F50" t="s">
+        <v>229</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0.62739999999999996</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0.48039999999999999</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0.15129999999999999</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0.41120000000000001</v>
+      </c>
+      <c r="K50" t="s">
+        <v>230</v>
+      </c>
       <c r="L50" s="14">
-        <v>4.4799999999999998E-5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+        <f>0.0002526</f>
+        <v>2.5260000000000001E-4</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>50</v>
       </c>
+      <c r="B51" s="1">
+        <v>0.84760000000000002</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0.50819999999999999</v>
+      </c>
+      <c r="D51" s="1">
+        <v>0.1671</v>
+      </c>
+      <c r="E51" s="1">
+        <v>0.4108</v>
+      </c>
+      <c r="F51" t="s">
+        <v>231</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0.60760000000000003</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0.54810000000000003</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0.1293</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0.40379999999999999</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>231</v>
+      </c>
       <c r="L51" s="14">
-        <v>2.26E-5</v>
+        <v>9.1769999999999997E-5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1">
+        <v>0.8357</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.52190000000000003</v>
+      </c>
+      <c r="D52" s="1">
+        <v>0.1608</v>
+      </c>
+      <c r="E52" s="1">
+        <v>0.41620000000000001</v>
+      </c>
+      <c r="F52" t="s">
+        <v>232</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0.60529999999999995</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0.55740000000000001</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0.1236</v>
+      </c>
+      <c r="J52" s="1">
+        <v>0.41549999999999998</v>
+      </c>
+      <c r="K52" t="s">
+        <v>233</v>
+      </c>
+      <c r="L52" s="14">
+        <v>4.104E-5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1">
+        <v>0.83179999999999998</v>
+      </c>
+      <c r="C53" s="1">
+        <v>0.52949999999999997</v>
+      </c>
+      <c r="D53" s="1">
+        <v>0.15670000000000001</v>
+      </c>
+      <c r="E53" s="1">
+        <v>0.42080000000000001</v>
+      </c>
+      <c r="F53" t="s">
+        <v>234</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0.61270000000000002</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0.56259999999999999</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0.12520000000000001</v>
+      </c>
+      <c r="J53" s="1">
+        <v>0.40839999999999999</v>
+      </c>
+      <c r="K53" t="s">
+        <v>235</v>
+      </c>
+      <c r="L53" s="14">
+        <v>4.0599999999999998E-5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1">
+        <v>0.8357</v>
+      </c>
+      <c r="C54" s="1">
+        <v>0.52969999999999995</v>
+      </c>
+      <c r="D54" s="1">
+        <v>0.15809999999999999</v>
+      </c>
+      <c r="E54" s="1">
+        <v>0.41760000000000003</v>
+      </c>
+      <c r="F54" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0.62260000000000004</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0.5716</v>
+      </c>
+      <c r="I54" s="1">
+        <v>0.1237</v>
+      </c>
+      <c r="J54" s="1">
+        <v>0.40239999999999998</v>
+      </c>
+      <c r="K54" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="L54" s="14">
+        <v>8.8830000000000002E-5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1">
+        <v>0.83540000000000003</v>
+      </c>
+      <c r="C55" s="1">
+        <v>0.52410000000000001</v>
+      </c>
+      <c r="D55" s="1">
+        <v>0.157</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0.4178</v>
+      </c>
+      <c r="F55" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0.53979999999999995</v>
+      </c>
+      <c r="I55" s="1">
+        <v>0.127</v>
+      </c>
+      <c r="J55" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="K55" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="L55" s="14">
+        <v>1.6540000000000001E-4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1">
+        <v>0.85209999999999997</v>
+      </c>
+      <c r="C56" s="1">
+        <v>0.49859999999999999</v>
+      </c>
+      <c r="D56" s="1">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="E56" s="1">
+        <v>0.40860000000000002</v>
+      </c>
+      <c r="F56" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0.63349999999999995</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0.51949999999999996</v>
+      </c>
+      <c r="I56" s="1">
+        <v>0.13750000000000001</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0.4042</v>
+      </c>
+      <c r="K56" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="L56" s="14">
+        <v>3.2190000000000002E-4</v>
+      </c>
+      <c r="M56" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1">
+        <v>0.84430000000000005</v>
+      </c>
+      <c r="C57" s="1">
+        <v>0.51359999999999995</v>
+      </c>
+      <c r="D57" s="1">
+        <v>0.16159999999999999</v>
+      </c>
+      <c r="E57" s="1">
+        <v>0.41120000000000001</v>
+      </c>
+      <c r="F57" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0.62629999999999997</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0.55389999999999995</v>
+      </c>
+      <c r="I57" s="1">
+        <v>0.1249</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0.40710000000000002</v>
+      </c>
+      <c r="K57" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="L57" s="14">
+        <v>2.8190000000000002E-4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1">
+        <v>0.84509999999999996</v>
+      </c>
+      <c r="C58" s="1">
+        <v>0.51380000000000003</v>
+      </c>
+      <c r="D58" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="E58" s="1">
+        <v>0.40910000000000002</v>
+      </c>
+      <c r="F58" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0.64149999999999996</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0.53580000000000005</v>
+      </c>
+      <c r="I58" s="1">
+        <v>0.13489999999999999</v>
+      </c>
+      <c r="J58" s="1">
+        <v>0.40389999999999998</v>
+      </c>
+      <c r="K58" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="L58" s="14">
+        <v>2.767E-4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1">
+        <v>0.83450000000000002</v>
+      </c>
+      <c r="C59" s="1">
+        <v>0.53149999999999997</v>
+      </c>
+      <c r="D59" s="1">
+        <v>0.153</v>
+      </c>
+      <c r="E59" s="1">
+        <v>0.41489999999999999</v>
+      </c>
+      <c r="F59" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0.63449999999999995</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0.54390000000000005</v>
+      </c>
+      <c r="I59" s="1">
+        <v>0.1333</v>
+      </c>
+      <c r="J59" s="1">
+        <v>0.40010000000000001</v>
+      </c>
+      <c r="K59" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="L59" s="14">
+        <v>2.264E-4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1">
+        <v>0.82469999999999999</v>
+      </c>
+      <c r="C60" s="1">
+        <v>0.54220000000000002</v>
+      </c>
+      <c r="D60" s="1">
+        <v>0.1469</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0.4219</v>
+      </c>
+      <c r="F60" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="G60" s="20">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0.5776</v>
+      </c>
+      <c r="I60" s="1">
+        <v>0.1164</v>
+      </c>
+      <c r="J60" s="1">
+        <v>0.41639999999999999</v>
+      </c>
+      <c r="K60" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L60" s="14">
+        <v>1.507E-4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1">
+        <v>0.81889999999999996</v>
+      </c>
+      <c r="C61" s="1">
+        <v>0.55379999999999996</v>
+      </c>
+      <c r="D61" s="1">
+        <v>0.1419</v>
+      </c>
+      <c r="E61" s="1">
+        <v>0.4269</v>
+      </c>
+      <c r="F61" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0.62960000000000005</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0.57250000000000001</v>
+      </c>
+      <c r="I61" s="1">
+        <v>0.1182</v>
+      </c>
+      <c r="J61" s="1">
+        <v>0.40639999999999998</v>
+      </c>
+      <c r="K61" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="L61" s="14">
+        <v>7.7990000000000004E-5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="L62" s="14">
+        <v>3.434E-5</v>
+      </c>
+      <c r="M62" s="21" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffinfarrow/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffin/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F003253-0E4D-7542-90E6-56686D6799F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEBFB59-195F-B44B-AA4D-F875E4D4CC3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20060" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17600" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
   <sheets>
     <sheet name="ResNet" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="262">
   <si>
     <t>Epoch</t>
   </si>
@@ -796,6 +796,36 @@
   </si>
   <si>
     <t>[0.7202 0.5434 0.7336 0.7123 0.6815]</t>
+  </si>
+  <si>
+    <t>[0.6761 0.5155 0.6655 0.6473 0.3746]</t>
+  </si>
+  <si>
+    <t>[0.7257 0.5334 0.7339 0.6930 0.7761]</t>
+  </si>
+  <si>
+    <t>[0.6675 0.5189 0.6620 0.6609 0.3546]</t>
+  </si>
+  <si>
+    <t>[0.7263 0.5197 0.7308 0.7122 0.7040]</t>
+  </si>
+  <si>
+    <t>[0.6515 0.5034 0.6603 0.6575 0.3434]</t>
+  </si>
+  <si>
+    <t>[0.6996 0.5172 0.7239 0.7152 0.7094]</t>
+  </si>
+  <si>
+    <t>[0.6634 0.5083 0.6593 0.6533 0.3423]</t>
+  </si>
+  <si>
+    <t>[0.7346 0.5466 0.7341 0.7323 0.7176]</t>
+  </si>
+  <si>
+    <t>[0.6575 0.5111 0.6549 0.6684 0.3498]</t>
+  </si>
+  <si>
+    <t>[0.7207 0.5102 0.7352 0.7216 0.7100]</t>
   </si>
 </sst>
 </file>
@@ -914,7 +944,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -942,9 +972,6 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3854,7 +3881,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{792EDA06-FC2C-024C-AE8E-C1CCD07C3F11}">
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5" style="1" customWidth="1"/>
@@ -5931,7 +5958,7 @@
       <c r="E54" s="1">
         <v>0.41760000000000003</v>
       </c>
-      <c r="F54" s="20" t="s">
+      <c r="F54" t="s">
         <v>236</v>
       </c>
       <c r="G54" s="1">
@@ -5946,7 +5973,7 @@
       <c r="J54" s="1">
         <v>0.40239999999999998</v>
       </c>
-      <c r="K54" s="20" t="s">
+      <c r="K54" t="s">
         <v>237</v>
       </c>
       <c r="L54" s="14">
@@ -5969,7 +5996,7 @@
       <c r="E55" s="1">
         <v>0.4178</v>
       </c>
-      <c r="F55" s="20" t="s">
+      <c r="F55" t="s">
         <v>238</v>
       </c>
       <c r="G55" s="1">
@@ -5984,7 +6011,7 @@
       <c r="J55" s="1">
         <v>0.41</v>
       </c>
-      <c r="K55" s="20" t="s">
+      <c r="K55" t="s">
         <v>239</v>
       </c>
       <c r="L55" s="14">
@@ -6007,7 +6034,7 @@
       <c r="E56" s="1">
         <v>0.40860000000000002</v>
       </c>
-      <c r="F56" s="20" t="s">
+      <c r="F56" t="s">
         <v>240</v>
       </c>
       <c r="G56" s="1">
@@ -6022,13 +6049,13 @@
       <c r="J56" s="1">
         <v>0.4042</v>
       </c>
-      <c r="K56" s="20" t="s">
+      <c r="K56" t="s">
         <v>241</v>
       </c>
       <c r="L56" s="14">
         <v>3.2190000000000002E-4</v>
       </c>
-      <c r="M56" s="21" t="s">
+      <c r="M56" s="16" t="s">
         <v>24</v>
       </c>
     </row>
@@ -6048,7 +6075,7 @@
       <c r="E57" s="1">
         <v>0.41120000000000001</v>
       </c>
-      <c r="F57" s="20" t="s">
+      <c r="F57" t="s">
         <v>242</v>
       </c>
       <c r="G57" s="1">
@@ -6063,7 +6090,7 @@
       <c r="J57" s="1">
         <v>0.40710000000000002</v>
       </c>
-      <c r="K57" s="20" t="s">
+      <c r="K57" t="s">
         <v>243</v>
       </c>
       <c r="L57" s="14">
@@ -6086,7 +6113,7 @@
       <c r="E58" s="1">
         <v>0.40910000000000002</v>
       </c>
-      <c r="F58" s="20" t="s">
+      <c r="F58" t="s">
         <v>244</v>
       </c>
       <c r="G58" s="1">
@@ -6101,7 +6128,7 @@
       <c r="J58" s="1">
         <v>0.40389999999999998</v>
       </c>
-      <c r="K58" s="20" t="s">
+      <c r="K58" t="s">
         <v>245</v>
       </c>
       <c r="L58" s="14">
@@ -6124,7 +6151,7 @@
       <c r="E59" s="1">
         <v>0.41489999999999999</v>
       </c>
-      <c r="F59" s="20" t="s">
+      <c r="F59" t="s">
         <v>246</v>
       </c>
       <c r="G59" s="1">
@@ -6139,7 +6166,7 @@
       <c r="J59" s="1">
         <v>0.40010000000000001</v>
       </c>
-      <c r="K59" s="20" t="s">
+      <c r="K59" t="s">
         <v>247</v>
       </c>
       <c r="L59" s="14">
@@ -6162,10 +6189,10 @@
       <c r="E60" s="1">
         <v>0.4219</v>
       </c>
-      <c r="F60" s="20" t="s">
+      <c r="F60" t="s">
         <v>248</v>
       </c>
-      <c r="G60" s="20">
+      <c r="G60">
         <v>0.61599999999999999</v>
       </c>
       <c r="H60" s="1">
@@ -6177,7 +6204,7 @@
       <c r="J60" s="1">
         <v>0.41639999999999999</v>
       </c>
-      <c r="K60" s="20" t="s">
+      <c r="K60" t="s">
         <v>249</v>
       </c>
       <c r="L60" s="14">
@@ -6200,7 +6227,7 @@
       <c r="E61" s="1">
         <v>0.4269</v>
       </c>
-      <c r="F61" s="20" t="s">
+      <c r="F61" t="s">
         <v>250</v>
       </c>
       <c r="G61" s="1">
@@ -6215,7 +6242,7 @@
       <c r="J61" s="1">
         <v>0.40639999999999998</v>
       </c>
-      <c r="K61" s="20" t="s">
+      <c r="K61" t="s">
         <v>251</v>
       </c>
       <c r="L61" s="14">
@@ -6226,11 +6253,193 @@
       <c r="A62" s="1">
         <v>61</v>
       </c>
+      <c r="B62" s="1">
+        <v>0.91069999999999995</v>
+      </c>
+      <c r="C62" s="1">
+        <v>0.4466</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0.19869999999999999</v>
+      </c>
+      <c r="E62" s="1">
+        <v>0.3851</v>
+      </c>
+      <c r="F62" t="s">
+        <v>252</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0.63570000000000004</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0.57050000000000001</v>
+      </c>
+      <c r="I62" s="1">
+        <v>0.1212</v>
+      </c>
+      <c r="J62" s="1">
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="K62" t="s">
+        <v>253</v>
+      </c>
       <c r="L62" s="14">
-        <v>3.434E-5</v>
-      </c>
-      <c r="M62" s="21" t="s">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M62" s="16" t="s">
         <v>228</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="C63" s="1">
+        <v>0.44390000000000002</v>
+      </c>
+      <c r="D63" s="1">
+        <v>0.20280000000000001</v>
+      </c>
+      <c r="E63" s="1">
+        <v>0.38119999999999998</v>
+      </c>
+      <c r="F63" t="s">
+        <v>254</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0.63819999999999999</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0.54579999999999995</v>
+      </c>
+      <c r="I63" s="1">
+        <v>0.128</v>
+      </c>
+      <c r="J63" s="1">
+        <v>0.40720000000000001</v>
+      </c>
+      <c r="K63" t="s">
+        <v>255</v>
+      </c>
+      <c r="L63" s="14">
+        <v>3.3429999999999997E-5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1">
+        <v>0.90710000000000002</v>
+      </c>
+      <c r="C64" s="1">
+        <v>0.42659999999999998</v>
+      </c>
+      <c r="D64" s="1">
+        <v>0.21279999999999999</v>
+      </c>
+      <c r="E64" s="1">
+        <v>0.3765</v>
+      </c>
+      <c r="F64" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0.63490000000000002</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0.55840000000000001</v>
+      </c>
+      <c r="I64" s="1">
+        <v>0.12820000000000001</v>
+      </c>
+      <c r="J64" s="1">
+        <v>0.3962</v>
+      </c>
+      <c r="K64" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="L64" s="14">
+        <v>7.1959999999999995E-5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1">
+        <v>0.90459999999999996</v>
+      </c>
+      <c r="C65" s="1">
+        <v>0.42770000000000002</v>
+      </c>
+      <c r="D65" s="1">
+        <v>0.2104</v>
+      </c>
+      <c r="E65" s="1">
+        <v>0.3765</v>
+      </c>
+      <c r="F65" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0.62060000000000004</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0.59709999999999996</v>
+      </c>
+      <c r="I65" s="1">
+        <v>0.1125</v>
+      </c>
+      <c r="J65" s="1">
+        <v>0.40060000000000001</v>
+      </c>
+      <c r="K65" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="L65" s="14">
+        <v>1.3180000000000001E-4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1">
+        <v>0.90439999999999998</v>
+      </c>
+      <c r="C66" s="1">
+        <v>0.41959999999999997</v>
+      </c>
+      <c r="D66" s="1">
+        <v>0.20910000000000001</v>
+      </c>
+      <c r="E66" s="1">
+        <v>0.37390000000000001</v>
+      </c>
+      <c r="F66" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0.62690000000000001</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0.56189999999999996</v>
+      </c>
+      <c r="I66" s="1">
+        <v>0.12540000000000001</v>
+      </c>
+      <c r="J66" s="1">
+        <v>0.39129999999999998</v>
+      </c>
+      <c r="K66" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="L66" s="14">
+        <v>1.8760000000000001E-4</v>
       </c>
     </row>
   </sheetData>

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffin/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffinfarrow/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEBFB59-195F-B44B-AA4D-F875E4D4CC3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39495080-5B59-1D4F-A504-8B087A8C418C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17600" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="266">
   <si>
     <t>Epoch</t>
   </si>
@@ -826,6 +826,18 @@
   </si>
   <si>
     <t>[0.7207 0.5102 0.7352 0.7216 0.7100]</t>
+  </si>
+  <si>
+    <t>[0.6601 0.4975 0.6572 0.6586 0.3399]</t>
+  </si>
+  <si>
+    <t>[0.7155 0.4757 0.7051 0.7332 0.7128]</t>
+  </si>
+  <si>
+    <t>Reset?</t>
+  </si>
+  <si>
+    <t>Have we over regularised? Results are a little weird and training is getting worse with each epoch</t>
   </si>
 </sst>
 </file>
@@ -944,7 +956,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -972,6 +984,9 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3881,7 +3896,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{792EDA06-FC2C-024C-AE8E-C1CCD07C3F11}">
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5" style="1" customWidth="1"/>
@@ -6344,7 +6359,7 @@
       <c r="E64" s="1">
         <v>0.3765</v>
       </c>
-      <c r="F64" s="20" t="s">
+      <c r="F64" t="s">
         <v>256</v>
       </c>
       <c r="G64" s="1">
@@ -6359,14 +6374,14 @@
       <c r="J64" s="1">
         <v>0.3962</v>
       </c>
-      <c r="K64" s="20" t="s">
+      <c r="K64" t="s">
         <v>257</v>
       </c>
       <c r="L64" s="14">
         <v>7.1959999999999995E-5</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -6382,7 +6397,7 @@
       <c r="E65" s="1">
         <v>0.3765</v>
       </c>
-      <c r="F65" s="20" t="s">
+      <c r="F65" t="s">
         <v>258</v>
       </c>
       <c r="G65" s="1">
@@ -6397,14 +6412,14 @@
       <c r="J65" s="1">
         <v>0.40060000000000001</v>
       </c>
-      <c r="K65" s="20" t="s">
+      <c r="K65" t="s">
         <v>259</v>
       </c>
       <c r="L65" s="14">
         <v>1.3180000000000001E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -6420,7 +6435,7 @@
       <c r="E66" s="1">
         <v>0.37390000000000001</v>
       </c>
-      <c r="F66" s="20" t="s">
+      <c r="F66" t="s">
         <v>260</v>
       </c>
       <c r="G66" s="1">
@@ -6435,11 +6450,57 @@
       <c r="J66" s="1">
         <v>0.39129999999999998</v>
       </c>
-      <c r="K66" s="20" t="s">
+      <c r="K66" t="s">
         <v>261</v>
       </c>
       <c r="L66" s="14">
         <v>1.8760000000000001E-4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1">
+        <v>0.90920000000000001</v>
+      </c>
+      <c r="C67" s="1">
+        <v>0.4194</v>
+      </c>
+      <c r="D67" s="1">
+        <v>0.2127</v>
+      </c>
+      <c r="E67" s="1">
+        <v>0.37230000000000002</v>
+      </c>
+      <c r="F67" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0.64580000000000004</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0.53410000000000002</v>
+      </c>
+      <c r="I67" s="1">
+        <v>0.1368</v>
+      </c>
+      <c r="J67" s="1">
+        <v>0.3952</v>
+      </c>
+      <c r="K67" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="L67" s="14">
+        <v>2.1709999999999999E-4</v>
+      </c>
+      <c r="M67" s="21" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="M68" s="21" t="s">
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffinfarrow/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39495080-5B59-1D4F-A504-8B087A8C418C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12255481-95CA-C14B-B980-56084C5B3D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17600" activeTab="3" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20060" activeTab="4" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
   <sheets>
     <sheet name="ResNet" sheetId="1" r:id="rId1"/>
     <sheet name="ResNet_Different_Loss" sheetId="3" r:id="rId2"/>
     <sheet name="EfficientNet" sheetId="2" r:id="rId3"/>
     <sheet name="EfficientNet-Retrain" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
+    <sheet name="Fixed learning rate scheduler" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="279">
   <si>
     <t>Epoch</t>
   </si>
@@ -838,13 +838,55 @@
   </si>
   <si>
     <t>Have we over regularised? Results are a little weird and training is getting worse with each epoch</t>
+  </si>
+  <si>
+    <t>[0.4243 0.3640 0.3818 0.4000 0.2075]</t>
+  </si>
+  <si>
+    <t>[0.5654 0.4644 0.4785 0.5042 0.3038]</t>
+  </si>
+  <si>
+    <t>[0.5957 0.4725 0.5333 0.5624 0.3451]</t>
+  </si>
+  <si>
+    <t>[0.6559 0.4377 0.6163 0.6300 0.4885]</t>
+  </si>
+  <si>
+    <t>[0.6434 0.5105 0.5842 0.6141 0.4419]</t>
+  </si>
+  <si>
+    <t>[0.7015 0.4683 0.6087 0.6204 0.5682]</t>
+  </si>
+  <si>
+    <t>[0.6593 0.5134 0.6164 0.6193 0.5028]</t>
+  </si>
+  <si>
+    <t>[0.6818 0.5544 0.5970 0.6559 0.7277]</t>
+  </si>
+  <si>
+    <t>[0.6708 0.5272 0.6378 0.6477 0.5440]</t>
+  </si>
+  <si>
+    <t>[0.6953 0.4958 0.6827 0.6941 0.7703]</t>
+  </si>
+  <si>
+    <t>[0.6790 0.5478 0.6479 0.6618 0.5693]</t>
+  </si>
+  <si>
+    <t>[0.6954 0.4779 0.7032 0.6966 0.7160]</t>
+  </si>
+  <si>
+    <t>Reset, start from scratch, mixed loss function, new learning rate scheduler, using adam w optimiser instead of adam</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -892,8 +934,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -906,8 +966,14 @@
         <bgColor theme="0" tint="-0.14999847407452621"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor theme="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -952,11 +1018,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -983,10 +1064,15 @@
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1877,7 +1963,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FCDFC6-C99C-D343-998E-FFAC6AB50B7A}">
   <dimension ref="A1:J29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="8.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" style="1" customWidth="1"/>
@@ -1891,7 +1977,7 @@
     <col min="10" max="10" width="24.33203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1923,7 +2009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" s="1">
         <v>6</v>
       </c>
@@ -1955,7 +2041,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="A3" s="1">
         <v>7</v>
       </c>
@@ -1987,7 +2073,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="1">
         <v>8</v>
       </c>
@@ -2019,7 +2105,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="1">
         <v>9</v>
       </c>
@@ -2051,7 +2137,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="1">
         <v>10</v>
       </c>
@@ -2083,7 +2169,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7" s="1">
         <v>11</v>
       </c>
@@ -2115,7 +2201,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" s="1">
         <v>12</v>
       </c>
@@ -2147,7 +2233,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="1">
         <v>13</v>
       </c>
@@ -2179,7 +2265,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="1">
         <v>14</v>
       </c>
@@ -2211,7 +2297,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="1">
         <v>15</v>
       </c>
@@ -2243,7 +2329,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="1">
         <v>16</v>
       </c>
@@ -2275,7 +2361,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="1">
         <v>17</v>
       </c>
@@ -2307,7 +2393,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="1">
         <v>18</v>
       </c>
@@ -2339,7 +2425,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="1">
         <v>19</v>
       </c>
@@ -2371,7 +2457,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="1">
         <v>20</v>
       </c>
@@ -2403,7 +2489,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="1">
         <v>21</v>
       </c>
@@ -2435,7 +2521,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="1">
         <v>22</v>
       </c>
@@ -2467,7 +2553,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="1">
         <v>23</v>
       </c>
@@ -2499,7 +2585,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="1">
         <v>24</v>
       </c>
@@ -2528,7 +2614,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="1">
         <v>25</v>
       </c>
@@ -2557,7 +2643,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>26</v>
       </c>
@@ -2586,7 +2672,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="1">
         <v>27</v>
       </c>
@@ -2615,7 +2701,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" s="1">
         <v>28</v>
       </c>
@@ -2644,7 +2730,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" s="1">
         <v>29</v>
       </c>
@@ -2676,7 +2762,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" s="1">
         <v>30</v>
       </c>
@@ -2705,7 +2791,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" s="1">
         <v>31</v>
       </c>
@@ -2734,7 +2820,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" s="1">
         <v>32</v>
       </c>
@@ -2763,7 +2849,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="1">
         <v>33</v>
       </c>
@@ -2803,9 +2889,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E03FEB-F26A-6948-8F66-30F9CC31F284}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" s="7">
         <v>23</v>
       </c>
@@ -2837,7 +2923,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" s="11">
         <v>24</v>
       </c>
@@ -2869,7 +2955,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="A3" s="7">
         <v>25</v>
       </c>
@@ -2901,7 +2987,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="11">
         <v>26</v>
       </c>
@@ -2933,7 +3019,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="7">
         <v>27</v>
       </c>
@@ -2965,7 +3051,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="11">
         <v>28</v>
       </c>
@@ -2997,7 +3083,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7" s="7">
         <v>29</v>
       </c>
@@ -3029,7 +3115,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" s="11">
         <v>30</v>
       </c>
@@ -3061,7 +3147,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="7">
         <v>31</v>
       </c>
@@ -3093,7 +3179,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="11">
         <v>32</v>
       </c>
@@ -3125,7 +3211,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="7">
         <v>33</v>
       </c>
@@ -3157,7 +3243,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="11">
         <v>34</v>
       </c>
@@ -3189,7 +3275,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="7">
         <v>35</v>
       </c>
@@ -3221,7 +3307,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="11">
         <v>36</v>
       </c>
@@ -3251,7 +3337,7 @@
       </c>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="7">
         <v>37</v>
       </c>
@@ -3289,7 +3375,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B641F396-8762-B74C-B488-26FE674E428C}">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="8.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" style="1" customWidth="1"/>
@@ -3303,7 +3389,7 @@
     <col min="10" max="10" width="24.33203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3335,7 +3421,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3364,7 +3450,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3393,7 +3479,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3422,7 +3508,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3451,7 +3537,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -3480,7 +3566,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -3509,7 +3595,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -3538,7 +3624,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -3567,7 +3653,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -3596,7 +3682,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -3625,7 +3711,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -3654,7 +3740,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -3683,32 +3769,32 @@
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -3718,7 +3804,7 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -3729,7 +3815,7 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -3740,7 +3826,7 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -3751,7 +3837,7 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -3762,7 +3848,7 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -3773,12 +3859,12 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -3787,27 +3873,27 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -3815,21 +3901,21 @@
       <c r="I31"/>
       <c r="J31"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="E32"/>
       <c r="I32"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="E33"/>
       <c r="I33"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -3838,42 +3924,42 @@
       <c r="I34"/>
       <c r="J34"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10">
       <c r="A35" s="1">
         <v>34</v>
       </c>
       <c r="E35"/>
       <c r="I35"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10">
       <c r="A36" s="1">
         <v>35</v>
       </c>
       <c r="E36"/>
       <c r="I36"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="E37"/>
       <c r="I37"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10">
       <c r="A38" s="1">
         <v>37</v>
       </c>
       <c r="E38"/>
       <c r="I38"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10">
       <c r="A39" s="1">
         <v>38</v>
       </c>
       <c r="E39"/>
       <c r="I39"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -3881,7 +3967,7 @@
       <c r="I40"/>
       <c r="J40"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -3897,7 +3983,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{792EDA06-FC2C-024C-AE8E-C1CCD07C3F11}">
   <dimension ref="A1:M68"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="8.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" style="1" customWidth="1"/>
@@ -3912,7 +3998,7 @@
     <col min="13" max="13" width="29.1640625" style="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="17">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3953,7 +4039,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="102">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3994,7 +4080,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -4032,7 +4118,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -4070,7 +4156,7 @@
         <v>4.0000000000000002E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -4108,7 +4194,7 @@
         <v>5.9999999999999995E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -4146,7 +4232,7 @@
         <v>8.0000000000000004E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -4184,7 +4270,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="119">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -4225,7 +4311,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -4263,7 +4349,7 @@
         <v>8.2200000000000003E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -4301,7 +4387,7 @@
         <v>8.0000000000000004E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -4339,7 +4425,7 @@
         <v>7.7780000000000004E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -4377,7 +4463,7 @@
         <v>7.5560000000000004E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -4415,7 +4501,7 @@
         <v>7.3329999999999999E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="17">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -4456,7 +4542,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -4494,7 +4580,7 @@
         <v>8.2220000000000004E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -4532,7 +4618,7 @@
         <v>8.0000000000000004E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -4570,7 +4656,7 @@
         <v>7.7780000000000004E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -4608,7 +4694,7 @@
         <v>7.5560000000000004E-4</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="17">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -4649,7 +4735,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -4687,7 +4773,7 @@
         <v>7.1120000000000005E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -4725,7 +4811,7 @@
         <v>6.8900000000000005E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -4763,7 +4849,7 @@
         <v>6.6680000000000005E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -4801,7 +4887,7 @@
         <v>6.4459999999999995E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -4839,7 +4925,7 @@
         <v>6.2239999999999995E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -4877,7 +4963,7 @@
         <v>6.0019999999999995E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" ht="34">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -4918,7 +5004,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -4956,7 +5042,7 @@
         <v>5.5579999999999996E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -4994,7 +5080,7 @@
         <v>5.3359999999999996E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -5032,7 +5118,7 @@
         <v>5.1139999999999996E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -5070,7 +5156,7 @@
         <v>4.8890000000000001E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -5108,7 +5194,7 @@
         <v>4.6670000000000001E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" ht="34">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -5149,7 +5235,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -5187,7 +5273,7 @@
         <v>4.2220000000000002E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -5225,7 +5311,7 @@
         <v>4.0000000000000002E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -5263,7 +5349,7 @@
         <v>3.7780000000000002E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -5301,7 +5387,7 @@
         <v>3.5560000000000002E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5339,7 +5425,7 @@
         <v>3.3340000000000003E-4</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" ht="17">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -5380,7 +5466,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -5418,7 +5504,7 @@
         <v>2.8899999999999998E-4</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -5456,7 +5542,7 @@
         <v>2.6679999999999998E-4</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -5494,7 +5580,7 @@
         <v>2.4459999999999998E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -5532,7 +5618,7 @@
         <v>2.2240000000000001E-4</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -5570,7 +5656,7 @@
         <v>2.0019999999999999E-4</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" ht="119">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -5611,7 +5697,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -5649,7 +5735,7 @@
         <v>1.7780000000000001E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -5687,7 +5773,7 @@
         <v>2.2159999999999999E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -5725,7 +5811,7 @@
         <v>2.6400000000000002E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -5763,7 +5849,7 @@
         <v>3.0479999999999998E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -5801,7 +5887,7 @@
         <v>2.8079999999999999E-4</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" ht="34">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -5843,7 +5929,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -5881,7 +5967,7 @@
         <v>9.1769999999999997E-5</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -5919,7 +6005,7 @@
         <v>4.104E-5</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -5957,7 +6043,7 @@
         <v>4.0599999999999998E-5</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -5995,7 +6081,7 @@
         <v>8.8830000000000002E-5</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -6033,7 +6119,7 @@
         <v>1.6540000000000001E-4</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" ht="17">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -6074,7 +6160,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -6112,7 +6198,7 @@
         <v>2.8190000000000002E-4</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -6150,7 +6236,7 @@
         <v>2.767E-4</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -6188,7 +6274,7 @@
         <v>2.264E-4</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -6226,7 +6312,7 @@
         <v>1.507E-4</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -6264,7 +6350,7 @@
         <v>7.7990000000000004E-5</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" ht="34">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -6305,7 +6391,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -6343,7 +6429,7 @@
         <v>3.3429999999999997E-5</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -6381,7 +6467,7 @@
         <v>7.1959999999999995E-5</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -6419,7 +6505,7 @@
         <v>1.3180000000000001E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -6457,7 +6543,7 @@
         <v>1.8760000000000001E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" ht="51">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -6473,7 +6559,7 @@
       <c r="E67" s="1">
         <v>0.37230000000000002</v>
       </c>
-      <c r="F67" s="20" t="s">
+      <c r="F67" t="s">
         <v>262</v>
       </c>
       <c r="G67" s="1">
@@ -6488,18 +6574,18 @@
       <c r="J67" s="1">
         <v>0.3952</v>
       </c>
-      <c r="K67" s="20" t="s">
+      <c r="K67" t="s">
         <v>263</v>
       </c>
       <c r="L67" s="14">
         <v>2.1709999999999999E-4</v>
       </c>
-      <c r="M67" s="21" t="s">
+      <c r="M67" s="16" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="M68" s="21" t="s">
+    <row r="68" spans="1:13" ht="17">
+      <c r="M68" s="16" t="s">
         <v>264</v>
       </c>
     </row>
@@ -6513,9 +6599,307 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAA60BDE-8BDA-914D-8879-8F477F3344B6}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="2" width="10.83203125" style="1"/>
+    <col min="3" max="3" width="13.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="61.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="M1" s="21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="22">
+        <v>1</v>
+      </c>
+      <c r="B2" s="22">
+        <v>0.91269999999999996</v>
+      </c>
+      <c r="C2" s="22">
+        <v>0.2681</v>
+      </c>
+      <c r="D2" s="22">
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="E2" s="22">
+        <v>0.18709999999999999</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="G2" s="22">
+        <v>0.80640000000000001</v>
+      </c>
+      <c r="H2" s="22">
+        <v>0.46660000000000001</v>
+      </c>
+      <c r="I2" s="22">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="J2" s="22">
+        <v>0.21060000000000001</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="L2" s="23">
+        <v>1E-4</v>
+      </c>
+      <c r="M2" s="22" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="22">
+        <v>2</v>
+      </c>
+      <c r="B3" s="22">
+        <v>0.72950000000000004</v>
+      </c>
+      <c r="C3" s="22">
+        <v>0.38840000000000002</v>
+      </c>
+      <c r="D3" s="22">
+        <v>0.223</v>
+      </c>
+      <c r="E3" s="22">
+        <v>0.27379999999999999</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="G3" s="22">
+        <v>0.62549999999999994</v>
+      </c>
+      <c r="H3" s="22">
+        <v>0.41970000000000002</v>
+      </c>
+      <c r="I3" s="22">
+        <v>0.18679999999999999</v>
+      </c>
+      <c r="J3" s="22">
+        <v>0.32969999999999999</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="L3" s="23">
+        <v>3.2499999999999999E-4</v>
+      </c>
+      <c r="M3" s="22"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="22">
+        <v>3</v>
+      </c>
+      <c r="B4" s="22">
+        <v>0.64449999999999996</v>
+      </c>
+      <c r="C4" s="22">
+        <v>0.42959999999999998</v>
+      </c>
+      <c r="D4" s="22">
+        <v>0.1903</v>
+      </c>
+      <c r="E4" s="22">
+        <v>0.31369999999999998</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="G4" s="22">
+        <v>0.56159999999999999</v>
+      </c>
+      <c r="H4" s="22">
+        <v>0.40250000000000002</v>
+      </c>
+      <c r="I4" s="22">
+        <v>0.18459999999999999</v>
+      </c>
+      <c r="J4" s="22">
+        <v>0.36230000000000001</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="L4" s="23">
+        <v>5.5000000000000003E-4</v>
+      </c>
+      <c r="M4" s="22"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="25">
+        <v>4</v>
+      </c>
+      <c r="B5" s="25">
+        <v>0.60809999999999997</v>
+      </c>
+      <c r="C5" s="25">
+        <v>0.45340000000000003</v>
+      </c>
+      <c r="D5" s="25">
+        <v>0.1777</v>
+      </c>
+      <c r="E5" s="25">
+        <v>0.32629999999999998</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="G5" s="25">
+        <v>0.58979999999999999</v>
+      </c>
+      <c r="H5" s="25">
+        <v>0.4657</v>
+      </c>
+      <c r="I5" s="25">
+        <v>0.15179999999999999</v>
+      </c>
+      <c r="J5" s="25">
+        <v>0.37280000000000002</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="L5" s="14">
+        <v>7.7499999999999997E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="25">
+        <v>5</v>
+      </c>
+      <c r="B6" s="25">
+        <v>0.57189999999999996</v>
+      </c>
+      <c r="C6" s="25">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="D6" s="25">
+        <v>0.16309999999999999</v>
+      </c>
+      <c r="E6" s="25">
+        <v>0.3468</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="G6" s="25">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="H6" s="25">
+        <v>0.53369999999999995</v>
+      </c>
+      <c r="I6" s="25">
+        <v>0.1363</v>
+      </c>
+      <c r="J6" s="25">
+        <v>0.37180000000000002</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="L6" s="14">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="25">
+        <v>6</v>
+      </c>
+      <c r="B7" s="25">
+        <v>0.54269999999999996</v>
+      </c>
+      <c r="C7" s="26">
+        <v>0.49149999999999999</v>
+      </c>
+      <c r="D7" s="25">
+        <v>0.15590000000000001</v>
+      </c>
+      <c r="E7" s="25">
+        <v>0.3533</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="G7" s="25">
+        <v>0.48549999999999999</v>
+      </c>
+      <c r="H7" s="25">
+        <v>0.50060000000000004</v>
+      </c>
+      <c r="I7" s="25">
+        <v>0.14510000000000001</v>
+      </c>
+      <c r="J7" s="25">
+        <v>0.39419999999999999</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="L7" s="14">
+        <v>9.7799999999999992E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="L8" s="14">
+        <v>9.1410000000000005E-4</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ecg_classification_model/training_progress.xlsx
+++ b/ecg_classification_model/training_progress.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/griffinfarrow/Documents/Data_Science_Projects/bhf_classification/ecg_classification_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12255481-95CA-C14B-B980-56084C5B3D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A9B2C1-EB9E-1349-8B7D-11914E7CF75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20060" activeTab="4" xr2:uid="{91BACCCC-FC76-354F-B9A7-49FE9C42D7A7}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="303">
   <si>
     <t>Epoch</t>
   </si>
@@ -877,6 +877,78 @@
   </si>
   <si>
     <t>Reset, start from scratch, mixed loss function, new learning rate scheduler, using adam w optimiser instead of adam</t>
+  </si>
+  <si>
+    <t>[0.6932 0.5597 0.6667 0.6797 0.6168]</t>
+  </si>
+  <si>
+    <t>[0.7189 0.4800 0.6303 0.6468 0.7284]</t>
+  </si>
+  <si>
+    <t>[0.6945 0.5732 0.6708 0.6800 0.6104]</t>
+  </si>
+  <si>
+    <t>[0.7148 0.5714 0.6929 0.7182 0.7164]</t>
+  </si>
+  <si>
+    <t>[0.7025 0.5913 0.6856 0.6949 0.6276]</t>
+  </si>
+  <si>
+    <t>[0.7122 0.5595 0.6858 0.6848 0.6969]</t>
+  </si>
+  <si>
+    <t>[0.7156 0.6073 0.6895 0.7234 0.6585]</t>
+  </si>
+  <si>
+    <t>[0.7007 0.5758 0.6743 0.7393 0.8110]</t>
+  </si>
+  <si>
+    <t>[0.7307 0.6370 0.7197 0.7343 0.7061]</t>
+  </si>
+  <si>
+    <t>[0.7112 0.5675 0.7247 0.7224 0.7972]</t>
+  </si>
+  <si>
+    <t>[0.7291 0.6569 0.7346 0.7466 0.7284]</t>
+  </si>
+  <si>
+    <t>[0.7059 0.5500 0.7023 0.7449 0.7609]</t>
+  </si>
+  <si>
+    <t>[0.7461 0.6745 0.7516 0.7663 0.7374]</t>
+  </si>
+  <si>
+    <t>[0.7208 0.5841 0.7217 0.7358 0.7812]</t>
+  </si>
+  <si>
+    <t>[0.7625 0.7153 0.7698 0.7792 0.7707]</t>
+  </si>
+  <si>
+    <t>[0.7204 0.5774 0.7053 0.7228 0.7847]</t>
+  </si>
+  <si>
+    <t>[0.7767 0.7191 0.7888 0.7937 0.7839]</t>
+  </si>
+  <si>
+    <t>[0.6907 0.5496 0.7189 0.7145 0.7879]</t>
+  </si>
+  <si>
+    <t>[0.7623 0.7138 0.7613 0.7678 0.7641]</t>
+  </si>
+  <si>
+    <t>[0.6934 0.5507 0.6987 0.7317 0.7674]</t>
+  </si>
+  <si>
+    <t>[0.7555 0.7037 0.7505 0.7688 0.7232]</t>
+  </si>
+  <si>
+    <t>[0.7014 0.5667 0.7052 0.7118 0.7874]</t>
+  </si>
+  <si>
+    <t>[0.7441 0.6720 0.7542 0.7477 0.7146]</t>
+  </si>
+  <si>
+    <t>[0.6851 0.5359 0.6962 0.7255 0.7679]</t>
   </si>
 </sst>
 </file>
@@ -884,7 +956,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -1037,7 +1109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1071,8 +1143,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6599,7 +6670,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAA60BDE-8BDA-914D-8879-8F477F3344B6}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="2" width="10.83203125" style="1"/>
@@ -6778,37 +6849,37 @@
       <c r="M4" s="22"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="25">
+      <c r="A5" s="22">
         <v>4</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="22">
         <v>0.60809999999999997</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="22">
         <v>0.45340000000000003</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="22">
         <v>0.1777</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="22">
         <v>0.32629999999999998</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="22" t="s">
         <v>272</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="22">
         <v>0.58979999999999999</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="22">
         <v>0.4657</v>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="22">
         <v>0.15179999999999999</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="22">
         <v>0.37280000000000002</v>
       </c>
-      <c r="K5" s="25" t="s">
+      <c r="K5" s="22" t="s">
         <v>273</v>
       </c>
       <c r="L5" s="14">
@@ -6816,37 +6887,37 @@
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="25">
+      <c r="A6" s="22">
         <v>5</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="22">
         <v>0.57189999999999996</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="22">
         <v>0.47699999999999998</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="22">
         <v>0.16309999999999999</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="22">
         <v>0.3468</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="22">
         <v>0.52900000000000003</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="22">
         <v>0.53369999999999995</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="22">
         <v>0.1363</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="22">
         <v>0.37180000000000002</v>
       </c>
-      <c r="K6" s="25" t="s">
+      <c r="K6" s="22" t="s">
         <v>275</v>
       </c>
       <c r="L6" s="14">
@@ -6854,37 +6925,37 @@
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="25">
+      <c r="A7" s="22">
         <v>6</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="22">
         <v>0.54269999999999996</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="25">
         <v>0.49149999999999999</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="22">
         <v>0.15590000000000001</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="22">
         <v>0.3533</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="22" t="s">
         <v>276</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="22">
         <v>0.48549999999999999</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="22">
         <v>0.50060000000000004</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="22">
         <v>0.14510000000000001</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="22">
         <v>0.39419999999999999</v>
       </c>
-      <c r="K7" s="25" t="s">
+      <c r="K7" s="22" t="s">
         <v>277</v>
       </c>
       <c r="L7" s="14">
@@ -6892,11 +6963,473 @@
       </c>
     </row>
     <row r="8" spans="1:13">
+      <c r="A8" s="22">
+        <v>7</v>
+      </c>
+      <c r="B8" s="22">
+        <v>0.51359999999999995</v>
+      </c>
+      <c r="C8" s="22">
+        <v>0.51080000000000003</v>
+      </c>
+      <c r="D8" s="22">
+        <v>0.1457</v>
+      </c>
+      <c r="E8" s="22">
+        <v>0.3649</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="G8" s="22">
+        <v>0.5212</v>
+      </c>
+      <c r="H8" s="22">
+        <v>0.43309999999999998</v>
+      </c>
+      <c r="I8" s="22">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="J8" s="22">
+        <v>0.37609999999999999</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>280</v>
+      </c>
       <c r="L8" s="14">
         <v>9.1410000000000005E-4</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="22">
+        <v>8</v>
+      </c>
+      <c r="B9" s="22">
+        <v>0.505</v>
+      </c>
+      <c r="C9" s="22">
+        <v>0.51649999999999996</v>
+      </c>
+      <c r="D9" s="22">
+        <v>0.14349999999999999</v>
+      </c>
+      <c r="E9" s="22">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G9" s="22">
+        <v>0.48199999999999998</v>
+      </c>
+      <c r="H9" s="22">
+        <v>0.55730000000000002</v>
+      </c>
+      <c r="I9" s="22">
+        <v>0.1217</v>
+      </c>
+      <c r="J9" s="22">
+        <v>0.3952</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="L9" s="14">
+        <v>8.1450000000000001E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="22">
+        <v>9</v>
+      </c>
+      <c r="B10" s="22">
+        <v>0.48039999999999999</v>
+      </c>
+      <c r="C10" s="22">
+        <v>0.53380000000000005</v>
+      </c>
+      <c r="D10" s="22">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="E10" s="22">
+        <v>0.377</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="G10" s="22">
+        <v>0.48570000000000002</v>
+      </c>
+      <c r="H10" s="22">
+        <v>0.51949999999999996</v>
+      </c>
+      <c r="I10" s="22">
+        <v>0.1361</v>
+      </c>
+      <c r="J10" s="22">
+        <v>0.39379999999999998</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="L10" s="14">
+        <v>6.891E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="22">
+        <v>10</v>
+      </c>
+      <c r="B11" s="22">
+        <v>0.44869999999999999</v>
+      </c>
+      <c r="C11" s="22">
+        <v>0.55420000000000003</v>
+      </c>
+      <c r="D11" s="22">
+        <v>0.1268</v>
+      </c>
+      <c r="E11" s="22">
+        <v>0.38729999999999998</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="G11" s="22">
+        <v>0.46870000000000001</v>
+      </c>
+      <c r="H11" s="22">
+        <v>0.54859999999999998</v>
+      </c>
+      <c r="I11" s="22">
+        <v>0.1239</v>
+      </c>
+      <c r="J11" s="22">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="L11" s="14">
+        <v>5.5000000000000003E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="22">
+        <v>11</v>
+      </c>
+      <c r="B12" s="22">
+        <v>0.41830000000000001</v>
+      </c>
+      <c r="C12" s="22">
+        <v>0.57979999999999998</v>
+      </c>
+      <c r="D12" s="22">
+        <v>0.1176</v>
+      </c>
+      <c r="E12" s="22">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="G12" s="22">
+        <v>0.48120000000000002</v>
+      </c>
+      <c r="H12" s="22">
+        <v>0.58409999999999995</v>
+      </c>
+      <c r="I12" s="22">
+        <v>0.1132</v>
+      </c>
+      <c r="J12" s="22">
+        <v>0.39090000000000003</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="L12" s="14">
+        <v>4.1090000000000001E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="22">
+        <v>12</v>
+      </c>
+      <c r="B13" s="22">
+        <v>0.39219999999999999</v>
+      </c>
+      <c r="C13" s="22">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="D13" s="22">
+        <v>0.1109</v>
+      </c>
+      <c r="E13" s="22">
+        <v>0.41189999999999999</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="G13" s="22">
+        <v>0.47910000000000003</v>
+      </c>
+      <c r="H13" s="22">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="I13" s="22">
+        <v>0.12559999999999999</v>
+      </c>
+      <c r="J13" s="22">
+        <v>0.40139999999999998</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="L13" s="14">
+        <v>2.855E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="22">
+        <v>13</v>
+      </c>
+      <c r="B14" s="22">
+        <v>0.3634</v>
+      </c>
+      <c r="C14" s="22">
+        <v>0.61860000000000004</v>
+      </c>
+      <c r="D14" s="22">
+        <v>0.1028</v>
+      </c>
+      <c r="E14" s="22">
+        <v>0.41860000000000003</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="G14" s="22">
+        <v>0.48259999999999997</v>
+      </c>
+      <c r="H14" s="22">
+        <v>0.58130000000000004</v>
+      </c>
+      <c r="I14" s="22">
+        <v>0.1147</v>
+      </c>
+      <c r="J14" s="22">
+        <v>0.4027</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="L14" s="14">
+        <v>1.8589999999999999E-4</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="22">
+        <v>14</v>
+      </c>
+      <c r="B15" s="22">
+        <v>0.32979999999999998</v>
+      </c>
+      <c r="C15" s="22">
+        <v>0.65159999999999996</v>
+      </c>
+      <c r="D15" s="22">
+        <v>9.3399999999999997E-2</v>
+      </c>
+      <c r="E15" s="22">
+        <v>0.43130000000000002</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="G15" s="22">
+        <v>0.51259999999999994</v>
+      </c>
+      <c r="H15" s="22">
+        <v>0.57440000000000002</v>
+      </c>
+      <c r="I15" s="22">
+        <v>0.1168</v>
+      </c>
+      <c r="J15" s="22">
+        <v>0.39929999999999999</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="L15" s="14">
+        <v>1.22E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="22">
+        <v>15</v>
+      </c>
+      <c r="B16" s="22">
+        <v>0.31730000000000003</v>
+      </c>
+      <c r="C16" s="22">
+        <v>0.66979999999999995</v>
+      </c>
+      <c r="D16" s="22">
+        <v>8.7400000000000005E-2</v>
+      </c>
+      <c r="E16" s="22">
+        <v>0.44269999999999998</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="G16" s="22">
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="H16" s="22">
+        <v>0.59250000000000003</v>
+      </c>
+      <c r="I16" s="22">
+        <v>0.1105</v>
+      </c>
+      <c r="J16" s="22">
+        <v>0.39129999999999998</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="L16" s="14">
+        <v>6.9999999999999994E-5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="22">
+        <v>16</v>
+      </c>
+      <c r="B17" s="22">
+        <v>0.33660000000000001</v>
+      </c>
+      <c r="C17" s="22">
+        <v>0.63970000000000005</v>
+      </c>
+      <c r="D17" s="22">
+        <v>6.2E-2</v>
+      </c>
+      <c r="E17" s="22">
+        <v>0.43309999999999998</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="G17" s="22">
+        <v>0.5625</v>
+      </c>
+      <c r="H17" s="22">
+        <v>0.58640000000000003</v>
+      </c>
+      <c r="I17" s="22">
+        <v>0.1162</v>
+      </c>
+      <c r="J17" s="22">
+        <v>0.38590000000000002</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="L17" s="14">
+        <v>2.275E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="22">
+        <v>17</v>
+      </c>
+      <c r="B18" s="22">
+        <v>0.3543</v>
+      </c>
+      <c r="C18" s="22">
+        <v>0.62450000000000006</v>
+      </c>
+      <c r="D18" s="22">
+        <v>0.1016</v>
+      </c>
+      <c r="E18" s="22">
+        <v>0.42770000000000002</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="G18" s="22">
+        <v>0.53039999999999998</v>
+      </c>
+      <c r="H18" s="22">
+        <v>0.56059999999999999</v>
+      </c>
+      <c r="I18" s="22">
+        <v>0.1195</v>
+      </c>
+      <c r="J18" s="22">
+        <v>0.3972</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="L18" s="14">
+        <v>3.8499999999999998E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="22">
+        <v>18</v>
+      </c>
+      <c r="B19" s="22">
+        <v>0.37590000000000001</v>
+      </c>
+      <c r="C19" s="22">
+        <v>0.6109</v>
+      </c>
+      <c r="D19" s="22">
+        <v>0.1062</v>
+      </c>
+      <c r="E19" s="22">
+        <v>0.41670000000000001</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="G19" s="22">
+        <v>0.54749999999999999</v>
+      </c>
+      <c r="H19" s="22">
+        <v>0.55049999999999999</v>
+      </c>
+      <c r="I19" s="22">
+        <v>0.12130000000000001</v>
+      </c>
+      <c r="J19" s="22">
+        <v>0.39879999999999999</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="L19" s="14">
+        <v>5.4250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="22">
+        <v>19</v>
+      </c>
+      <c r="L20" s="14">
+        <v>6.9999999999999999E-4</v>
       </c>
     </row>
   </sheetData>
